--- a/runs/sample_1.xlsx
+++ b/runs/sample_1.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status" sheetId="1" r:id="Rd802a3e604164545"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Qubits" sheetId="2" r:id="Ra5462a975b31481e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estimates" sheetId="3" r:id="R0fb915c89f424bbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="4" r:id="Rb0042b930f2b49c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status" sheetId="1" r:id="Rdad1d78bb6834ee8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Qubits" sheetId="2" r:id="R397ae31dc0e1477e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estimates" sheetId="3" r:id="R33cb516e7c004527"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="4" r:id="R7134d5f748ad44da"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,12 +64,27 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2C6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF1F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF243C5A"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -108,7 +123,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -178,6 +193,26 @@
     </x:xf>
     <x:xf numFmtId="205" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -188,7 +223,7 @@
         <x:color rgb="FF276749"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE5F3E8"/>
         </x:patternFill>
       </x:fill>
@@ -198,7 +233,7 @@
         <x:color rgb="FF276749"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE5F3E8"/>
         </x:patternFill>
       </x:fill>
@@ -209,7 +244,7 @@
         <x:color rgb="FFA61B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -220,7 +255,7 @@
         <x:color rgb="FFA61B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -543,10 +578,15 @@
       </x:c>
       <x:c r="B8" s="6"/>
       <x:c r="C8" s="2"/>
-      <x:c r="D8" s="2"/>
-      <x:c r="E8" s="2"/>
-      <x:c r="F8" s="2"/>
-      <x:c r="G8" s="2"/>
+      <x:c r="D8" s="29" t="str">
+        <x:v>CSV export check</x:v>
+      </x:c>
+      <x:c r="E8" s="30" t="str">
+        <x:f>IF($B$4="","Set circuit ID",IF(OR(NOT(ISNUMBER($B$5)),$B$5&lt;=0),"Set target count",IF(E10&lt;&gt;$B$5,"Check qubit list",IF(E17&gt;0,"Duplicate qubits",IF(E16&gt;0,"Duplicate estimates",IF(OR(AND($B$13&lt;&gt;"MPS",$B$13&lt;&gt;"PPS"),NOT(ISNUMBER($B$14)),$B$14&lt;1,$B$14&gt;3),"Choose method and slot",IF(E21&lt;&gt;$B$5,"Missing selected values","Ready for template check")))))))</x:f>
+        <x:v>Set circuit ID</x:v>
+      </x:c>
+      <x:c r="F8" s="29"/>
+      <x:c r="G8" s="29"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="2" t="str">
@@ -613,8 +653,10 @@
       <x:c r="G12" s="2"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="2"/>
-      <x:c r="B13" s="2"/>
+      <x:c r="A13" s="2" t="str">
+        <x:v>CSV method</x:v>
+      </x:c>
+      <x:c r="B13" s="28"/>
       <x:c r="C13" s="2"/>
       <x:c r="D13" s="2" t="str">
         <x:v>PPS latest rows</x:v>
@@ -627,8 +669,10 @@
       <x:c r="G13" s="2"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="2"/>
-      <x:c r="B14" s="2"/>
+      <x:c r="A14" s="2" t="str">
+        <x:v>CSV precision slot</x:v>
+      </x:c>
+      <x:c r="B14" s="28"/>
       <x:c r="C14" s="2"/>
       <x:c r="D14" s="2" t="str">
         <x:v>MPS converging qubits</x:v>
@@ -728,8 +772,13 @@
       <x:c r="A21" s="2"/>
       <x:c r="B21" s="2"/>
       <x:c r="C21" s="2"/>
-      <x:c r="D21" s="2"/>
-      <x:c r="E21" s="2"/>
+      <x:c r="D21" s="2" t="str">
+        <x:v>CSV selected rows</x:v>
+      </x:c>
+      <x:c r="E21" s="2" t="n">
+        <x:f>COUNT('Qubits'!$T$6:$T$165)</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="F21" s="2"/>
       <x:c r="G21" s="2"/>
     </x:row>
@@ -821,9 +870,16 @@
       <x:c r="G28" s="16"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="1">
+  <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="B7">
       <x:formula1>"Continue,Move on"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="B13">
+      <x:formula1>"MPS,PPS"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B14">
+      <x:formula1>1</x:formula1>
+      <x:formula2>3</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -856,6 +912,7 @@
     <x:col min="17" max="17" width="15" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="15" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="22" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1002,6 +1059,9 @@
       <x:c r="S5" s="19" t="str">
         <x:v>Issue</x:v>
       </x:c>
+      <x:c r="T5" s="34" t="str">
+        <x:v>CSV estimate</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="6"/>
@@ -1057,6 +1117,9 @@
       <x:c r="S6" s="2" t="str">
         <x:f>IF(COUNTA(A6)=0,"",IF(COUNTIFS($A$6:$A$165,A6)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T6" s="23" t="str">
+        <x:f>IF(COUNTA($A6)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C6),C6,""),IF('Status'!$B$14=2,IF(ISNUMBER(D6),D6,""),IF('Status'!$B$14=3,IF(ISNUMBER(E6),E6,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J6),J6,""),IF('Status'!$B$14=2,IF(ISNUMBER(K6),K6,""),IF('Status'!$B$14=3,IF(ISNUMBER(L6),L6,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="6"/>
@@ -1112,6 +1175,9 @@
       <x:c r="S7" s="2" t="str">
         <x:f>IF(COUNTA(A7)=0,"",IF(COUNTIFS($A$6:$A$165,A7)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T7" s="23" t="str">
+        <x:f>IF(COUNTA($A7)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C7),C7,""),IF('Status'!$B$14=2,IF(ISNUMBER(D7),D7,""),IF('Status'!$B$14=3,IF(ISNUMBER(E7),E7,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J7),J7,""),IF('Status'!$B$14=2,IF(ISNUMBER(K7),K7,""),IF('Status'!$B$14=3,IF(ISNUMBER(L7),L7,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="6"/>
@@ -1167,6 +1233,9 @@
       <x:c r="S8" s="2" t="str">
         <x:f>IF(COUNTA(A8)=0,"",IF(COUNTIFS($A$6:$A$165,A8)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T8" s="23" t="str">
+        <x:f>IF(COUNTA($A8)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C8),C8,""),IF('Status'!$B$14=2,IF(ISNUMBER(D8),D8,""),IF('Status'!$B$14=3,IF(ISNUMBER(E8),E8,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J8),J8,""),IF('Status'!$B$14=2,IF(ISNUMBER(K8),K8,""),IF('Status'!$B$14=3,IF(ISNUMBER(L8),L8,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="6"/>
@@ -1222,6 +1291,9 @@
       <x:c r="S9" s="2" t="str">
         <x:f>IF(COUNTA(A9)=0,"",IF(COUNTIFS($A$6:$A$165,A9)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T9" s="23" t="str">
+        <x:f>IF(COUNTA($A9)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C9),C9,""),IF('Status'!$B$14=2,IF(ISNUMBER(D9),D9,""),IF('Status'!$B$14=3,IF(ISNUMBER(E9),E9,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J9),J9,""),IF('Status'!$B$14=2,IF(ISNUMBER(K9),K9,""),IF('Status'!$B$14=3,IF(ISNUMBER(L9),L9,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="6"/>
@@ -1277,6 +1349,9 @@
       <x:c r="S10" s="2" t="str">
         <x:f>IF(COUNTA(A10)=0,"",IF(COUNTIFS($A$6:$A$165,A10)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T10" s="23" t="str">
+        <x:f>IF(COUNTA($A10)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C10),C10,""),IF('Status'!$B$14=2,IF(ISNUMBER(D10),D10,""),IF('Status'!$B$14=3,IF(ISNUMBER(E10),E10,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J10),J10,""),IF('Status'!$B$14=2,IF(ISNUMBER(K10),K10,""),IF('Status'!$B$14=3,IF(ISNUMBER(L10),L10,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="6"/>
@@ -1332,6 +1407,9 @@
       <x:c r="S11" s="2" t="str">
         <x:f>IF(COUNTA(A11)=0,"",IF(COUNTIFS($A$6:$A$165,A11)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T11" s="23" t="str">
+        <x:f>IF(COUNTA($A11)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C11),C11,""),IF('Status'!$B$14=2,IF(ISNUMBER(D11),D11,""),IF('Status'!$B$14=3,IF(ISNUMBER(E11),E11,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J11),J11,""),IF('Status'!$B$14=2,IF(ISNUMBER(K11),K11,""),IF('Status'!$B$14=3,IF(ISNUMBER(L11),L11,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="6"/>
@@ -1387,6 +1465,9 @@
       <x:c r="S12" s="2" t="str">
         <x:f>IF(COUNTA(A12)=0,"",IF(COUNTIFS($A$6:$A$165,A12)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T12" s="23" t="str">
+        <x:f>IF(COUNTA($A12)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C12),C12,""),IF('Status'!$B$14=2,IF(ISNUMBER(D12),D12,""),IF('Status'!$B$14=3,IF(ISNUMBER(E12),E12,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J12),J12,""),IF('Status'!$B$14=2,IF(ISNUMBER(K12),K12,""),IF('Status'!$B$14=3,IF(ISNUMBER(L12),L12,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="6"/>
@@ -1442,6 +1523,9 @@
       <x:c r="S13" s="2" t="str">
         <x:f>IF(COUNTA(A13)=0,"",IF(COUNTIFS($A$6:$A$165,A13)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T13" s="23" t="str">
+        <x:f>IF(COUNTA($A13)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C13),C13,""),IF('Status'!$B$14=2,IF(ISNUMBER(D13),D13,""),IF('Status'!$B$14=3,IF(ISNUMBER(E13),E13,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J13),J13,""),IF('Status'!$B$14=2,IF(ISNUMBER(K13),K13,""),IF('Status'!$B$14=3,IF(ISNUMBER(L13),L13,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="6"/>
@@ -1497,6 +1581,9 @@
       <x:c r="S14" s="2" t="str">
         <x:f>IF(COUNTA(A14)=0,"",IF(COUNTIFS($A$6:$A$165,A14)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T14" s="23" t="str">
+        <x:f>IF(COUNTA($A14)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C14),C14,""),IF('Status'!$B$14=2,IF(ISNUMBER(D14),D14,""),IF('Status'!$B$14=3,IF(ISNUMBER(E14),E14,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J14),J14,""),IF('Status'!$B$14=2,IF(ISNUMBER(K14),K14,""),IF('Status'!$B$14=3,IF(ISNUMBER(L14),L14,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="6"/>
@@ -1552,6 +1639,9 @@
       <x:c r="S15" s="2" t="str">
         <x:f>IF(COUNTA(A15)=0,"",IF(COUNTIFS($A$6:$A$165,A15)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T15" s="23" t="str">
+        <x:f>IF(COUNTA($A15)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C15),C15,""),IF('Status'!$B$14=2,IF(ISNUMBER(D15),D15,""),IF('Status'!$B$14=3,IF(ISNUMBER(E15),E15,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J15),J15,""),IF('Status'!$B$14=2,IF(ISNUMBER(K15),K15,""),IF('Status'!$B$14=3,IF(ISNUMBER(L15),L15,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="6"/>
@@ -1607,6 +1697,9 @@
       <x:c r="S16" s="2" t="str">
         <x:f>IF(COUNTA(A16)=0,"",IF(COUNTIFS($A$6:$A$165,A16)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T16" s="23" t="str">
+        <x:f>IF(COUNTA($A16)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C16),C16,""),IF('Status'!$B$14=2,IF(ISNUMBER(D16),D16,""),IF('Status'!$B$14=3,IF(ISNUMBER(E16),E16,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J16),J16,""),IF('Status'!$B$14=2,IF(ISNUMBER(K16),K16,""),IF('Status'!$B$14=3,IF(ISNUMBER(L16),L16,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="6"/>
@@ -1662,6 +1755,9 @@
       <x:c r="S17" s="2" t="str">
         <x:f>IF(COUNTA(A17)=0,"",IF(COUNTIFS($A$6:$A$165,A17)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T17" s="23" t="str">
+        <x:f>IF(COUNTA($A17)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C17),C17,""),IF('Status'!$B$14=2,IF(ISNUMBER(D17),D17,""),IF('Status'!$B$14=3,IF(ISNUMBER(E17),E17,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J17),J17,""),IF('Status'!$B$14=2,IF(ISNUMBER(K17),K17,""),IF('Status'!$B$14=3,IF(ISNUMBER(L17),L17,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="6"/>
@@ -1717,6 +1813,9 @@
       <x:c r="S18" s="2" t="str">
         <x:f>IF(COUNTA(A18)=0,"",IF(COUNTIFS($A$6:$A$165,A18)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T18" s="23" t="str">
+        <x:f>IF(COUNTA($A18)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C18),C18,""),IF('Status'!$B$14=2,IF(ISNUMBER(D18),D18,""),IF('Status'!$B$14=3,IF(ISNUMBER(E18),E18,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J18),J18,""),IF('Status'!$B$14=2,IF(ISNUMBER(K18),K18,""),IF('Status'!$B$14=3,IF(ISNUMBER(L18),L18,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="6"/>
@@ -1772,6 +1871,9 @@
       <x:c r="S19" s="2" t="str">
         <x:f>IF(COUNTA(A19)=0,"",IF(COUNTIFS($A$6:$A$165,A19)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T19" s="23" t="str">
+        <x:f>IF(COUNTA($A19)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C19),C19,""),IF('Status'!$B$14=2,IF(ISNUMBER(D19),D19,""),IF('Status'!$B$14=3,IF(ISNUMBER(E19),E19,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J19),J19,""),IF('Status'!$B$14=2,IF(ISNUMBER(K19),K19,""),IF('Status'!$B$14=3,IF(ISNUMBER(L19),L19,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="6"/>
@@ -1827,6 +1929,9 @@
       <x:c r="S20" s="2" t="str">
         <x:f>IF(COUNTA(A20)=0,"",IF(COUNTIFS($A$6:$A$165,A20)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T20" s="23" t="str">
+        <x:f>IF(COUNTA($A20)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C20),C20,""),IF('Status'!$B$14=2,IF(ISNUMBER(D20),D20,""),IF('Status'!$B$14=3,IF(ISNUMBER(E20),E20,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J20),J20,""),IF('Status'!$B$14=2,IF(ISNUMBER(K20),K20,""),IF('Status'!$B$14=3,IF(ISNUMBER(L20),L20,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="6"/>
@@ -1882,6 +1987,9 @@
       <x:c r="S21" s="2" t="str">
         <x:f>IF(COUNTA(A21)=0,"",IF(COUNTIFS($A$6:$A$165,A21)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T21" s="23" t="str">
+        <x:f>IF(COUNTA($A21)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C21),C21,""),IF('Status'!$B$14=2,IF(ISNUMBER(D21),D21,""),IF('Status'!$B$14=3,IF(ISNUMBER(E21),E21,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J21),J21,""),IF('Status'!$B$14=2,IF(ISNUMBER(K21),K21,""),IF('Status'!$B$14=3,IF(ISNUMBER(L21),L21,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="6"/>
@@ -1937,6 +2045,9 @@
       <x:c r="S22" s="2" t="str">
         <x:f>IF(COUNTA(A22)=0,"",IF(COUNTIFS($A$6:$A$165,A22)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T22" s="23" t="str">
+        <x:f>IF(COUNTA($A22)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C22),C22,""),IF('Status'!$B$14=2,IF(ISNUMBER(D22),D22,""),IF('Status'!$B$14=3,IF(ISNUMBER(E22),E22,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J22),J22,""),IF('Status'!$B$14=2,IF(ISNUMBER(K22),K22,""),IF('Status'!$B$14=3,IF(ISNUMBER(L22),L22,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="6"/>
@@ -1992,6 +2103,9 @@
       <x:c r="S23" s="2" t="str">
         <x:f>IF(COUNTA(A23)=0,"",IF(COUNTIFS($A$6:$A$165,A23)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T23" s="23" t="str">
+        <x:f>IF(COUNTA($A23)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C23),C23,""),IF('Status'!$B$14=2,IF(ISNUMBER(D23),D23,""),IF('Status'!$B$14=3,IF(ISNUMBER(E23),E23,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J23),J23,""),IF('Status'!$B$14=2,IF(ISNUMBER(K23),K23,""),IF('Status'!$B$14=3,IF(ISNUMBER(L23),L23,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="6"/>
@@ -2047,6 +2161,9 @@
       <x:c r="S24" s="2" t="str">
         <x:f>IF(COUNTA(A24)=0,"",IF(COUNTIFS($A$6:$A$165,A24)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T24" s="23" t="str">
+        <x:f>IF(COUNTA($A24)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C24),C24,""),IF('Status'!$B$14=2,IF(ISNUMBER(D24),D24,""),IF('Status'!$B$14=3,IF(ISNUMBER(E24),E24,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J24),J24,""),IF('Status'!$B$14=2,IF(ISNUMBER(K24),K24,""),IF('Status'!$B$14=3,IF(ISNUMBER(L24),L24,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="6"/>
@@ -2102,6 +2219,9 @@
       <x:c r="S25" s="2" t="str">
         <x:f>IF(COUNTA(A25)=0,"",IF(COUNTIFS($A$6:$A$165,A25)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T25" s="23" t="str">
+        <x:f>IF(COUNTA($A25)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C25),C25,""),IF('Status'!$B$14=2,IF(ISNUMBER(D25),D25,""),IF('Status'!$B$14=3,IF(ISNUMBER(E25),E25,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J25),J25,""),IF('Status'!$B$14=2,IF(ISNUMBER(K25),K25,""),IF('Status'!$B$14=3,IF(ISNUMBER(L25),L25,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="6"/>
@@ -2157,6 +2277,9 @@
       <x:c r="S26" s="2" t="str">
         <x:f>IF(COUNTA(A26)=0,"",IF(COUNTIFS($A$6:$A$165,A26)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T26" s="23" t="str">
+        <x:f>IF(COUNTA($A26)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C26),C26,""),IF('Status'!$B$14=2,IF(ISNUMBER(D26),D26,""),IF('Status'!$B$14=3,IF(ISNUMBER(E26),E26,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J26),J26,""),IF('Status'!$B$14=2,IF(ISNUMBER(K26),K26,""),IF('Status'!$B$14=3,IF(ISNUMBER(L26),L26,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="6"/>
@@ -2212,6 +2335,9 @@
       <x:c r="S27" s="2" t="str">
         <x:f>IF(COUNTA(A27)=0,"",IF(COUNTIFS($A$6:$A$165,A27)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T27" s="23" t="str">
+        <x:f>IF(COUNTA($A27)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C27),C27,""),IF('Status'!$B$14=2,IF(ISNUMBER(D27),D27,""),IF('Status'!$B$14=3,IF(ISNUMBER(E27),E27,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J27),J27,""),IF('Status'!$B$14=2,IF(ISNUMBER(K27),K27,""),IF('Status'!$B$14=3,IF(ISNUMBER(L27),L27,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="6"/>
@@ -2267,6 +2393,9 @@
       <x:c r="S28" s="2" t="str">
         <x:f>IF(COUNTA(A28)=0,"",IF(COUNTIFS($A$6:$A$165,A28)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T28" s="23" t="str">
+        <x:f>IF(COUNTA($A28)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C28),C28,""),IF('Status'!$B$14=2,IF(ISNUMBER(D28),D28,""),IF('Status'!$B$14=3,IF(ISNUMBER(E28),E28,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J28),J28,""),IF('Status'!$B$14=2,IF(ISNUMBER(K28),K28,""),IF('Status'!$B$14=3,IF(ISNUMBER(L28),L28,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="6"/>
@@ -2322,6 +2451,9 @@
       <x:c r="S29" s="2" t="str">
         <x:f>IF(COUNTA(A29)=0,"",IF(COUNTIFS($A$6:$A$165,A29)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T29" s="23" t="str">
+        <x:f>IF(COUNTA($A29)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C29),C29,""),IF('Status'!$B$14=2,IF(ISNUMBER(D29),D29,""),IF('Status'!$B$14=3,IF(ISNUMBER(E29),E29,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J29),J29,""),IF('Status'!$B$14=2,IF(ISNUMBER(K29),K29,""),IF('Status'!$B$14=3,IF(ISNUMBER(L29),L29,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="6"/>
@@ -2377,6 +2509,9 @@
       <x:c r="S30" s="2" t="str">
         <x:f>IF(COUNTA(A30)=0,"",IF(COUNTIFS($A$6:$A$165,A30)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T30" s="23" t="str">
+        <x:f>IF(COUNTA($A30)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C30),C30,""),IF('Status'!$B$14=2,IF(ISNUMBER(D30),D30,""),IF('Status'!$B$14=3,IF(ISNUMBER(E30),E30,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J30),J30,""),IF('Status'!$B$14=2,IF(ISNUMBER(K30),K30,""),IF('Status'!$B$14=3,IF(ISNUMBER(L30),L30,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="6"/>
@@ -2432,6 +2567,9 @@
       <x:c r="S31" s="2" t="str">
         <x:f>IF(COUNTA(A31)=0,"",IF(COUNTIFS($A$6:$A$165,A31)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T31" s="23" t="str">
+        <x:f>IF(COUNTA($A31)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C31),C31,""),IF('Status'!$B$14=2,IF(ISNUMBER(D31),D31,""),IF('Status'!$B$14=3,IF(ISNUMBER(E31),E31,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J31),J31,""),IF('Status'!$B$14=2,IF(ISNUMBER(K31),K31,""),IF('Status'!$B$14=3,IF(ISNUMBER(L31),L31,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="6"/>
@@ -2487,6 +2625,9 @@
       <x:c r="S32" s="2" t="str">
         <x:f>IF(COUNTA(A32)=0,"",IF(COUNTIFS($A$6:$A$165,A32)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T32" s="23" t="str">
+        <x:f>IF(COUNTA($A32)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C32),C32,""),IF('Status'!$B$14=2,IF(ISNUMBER(D32),D32,""),IF('Status'!$B$14=3,IF(ISNUMBER(E32),E32,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J32),J32,""),IF('Status'!$B$14=2,IF(ISNUMBER(K32),K32,""),IF('Status'!$B$14=3,IF(ISNUMBER(L32),L32,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="6"/>
@@ -2542,6 +2683,9 @@
       <x:c r="S33" s="2" t="str">
         <x:f>IF(COUNTA(A33)=0,"",IF(COUNTIFS($A$6:$A$165,A33)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T33" s="23" t="str">
+        <x:f>IF(COUNTA($A33)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C33),C33,""),IF('Status'!$B$14=2,IF(ISNUMBER(D33),D33,""),IF('Status'!$B$14=3,IF(ISNUMBER(E33),E33,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J33),J33,""),IF('Status'!$B$14=2,IF(ISNUMBER(K33),K33,""),IF('Status'!$B$14=3,IF(ISNUMBER(L33),L33,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="6"/>
@@ -2597,6 +2741,9 @@
       <x:c r="S34" s="2" t="str">
         <x:f>IF(COUNTA(A34)=0,"",IF(COUNTIFS($A$6:$A$165,A34)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T34" s="23" t="str">
+        <x:f>IF(COUNTA($A34)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C34),C34,""),IF('Status'!$B$14=2,IF(ISNUMBER(D34),D34,""),IF('Status'!$B$14=3,IF(ISNUMBER(E34),E34,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J34),J34,""),IF('Status'!$B$14=2,IF(ISNUMBER(K34),K34,""),IF('Status'!$B$14=3,IF(ISNUMBER(L34),L34,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="6"/>
@@ -2652,6 +2799,9 @@
       <x:c r="S35" s="2" t="str">
         <x:f>IF(COUNTA(A35)=0,"",IF(COUNTIFS($A$6:$A$165,A35)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T35" s="23" t="str">
+        <x:f>IF(COUNTA($A35)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C35),C35,""),IF('Status'!$B$14=2,IF(ISNUMBER(D35),D35,""),IF('Status'!$B$14=3,IF(ISNUMBER(E35),E35,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J35),J35,""),IF('Status'!$B$14=2,IF(ISNUMBER(K35),K35,""),IF('Status'!$B$14=3,IF(ISNUMBER(L35),L35,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="6"/>
@@ -2707,6 +2857,9 @@
       <x:c r="S36" s="2" t="str">
         <x:f>IF(COUNTA(A36)=0,"",IF(COUNTIFS($A$6:$A$165,A36)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T36" s="23" t="str">
+        <x:f>IF(COUNTA($A36)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C36),C36,""),IF('Status'!$B$14=2,IF(ISNUMBER(D36),D36,""),IF('Status'!$B$14=3,IF(ISNUMBER(E36),E36,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J36),J36,""),IF('Status'!$B$14=2,IF(ISNUMBER(K36),K36,""),IF('Status'!$B$14=3,IF(ISNUMBER(L36),L36,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="6"/>
@@ -2762,6 +2915,9 @@
       <x:c r="S37" s="2" t="str">
         <x:f>IF(COUNTA(A37)=0,"",IF(COUNTIFS($A$6:$A$165,A37)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T37" s="23" t="str">
+        <x:f>IF(COUNTA($A37)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C37),C37,""),IF('Status'!$B$14=2,IF(ISNUMBER(D37),D37,""),IF('Status'!$B$14=3,IF(ISNUMBER(E37),E37,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J37),J37,""),IF('Status'!$B$14=2,IF(ISNUMBER(K37),K37,""),IF('Status'!$B$14=3,IF(ISNUMBER(L37),L37,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="6"/>
@@ -2817,6 +2973,9 @@
       <x:c r="S38" s="2" t="str">
         <x:f>IF(COUNTA(A38)=0,"",IF(COUNTIFS($A$6:$A$165,A38)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T38" s="23" t="str">
+        <x:f>IF(COUNTA($A38)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C38),C38,""),IF('Status'!$B$14=2,IF(ISNUMBER(D38),D38,""),IF('Status'!$B$14=3,IF(ISNUMBER(E38),E38,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J38),J38,""),IF('Status'!$B$14=2,IF(ISNUMBER(K38),K38,""),IF('Status'!$B$14=3,IF(ISNUMBER(L38),L38,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="6"/>
@@ -2872,6 +3031,9 @@
       <x:c r="S39" s="2" t="str">
         <x:f>IF(COUNTA(A39)=0,"",IF(COUNTIFS($A$6:$A$165,A39)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T39" s="23" t="str">
+        <x:f>IF(COUNTA($A39)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C39),C39,""),IF('Status'!$B$14=2,IF(ISNUMBER(D39),D39,""),IF('Status'!$B$14=3,IF(ISNUMBER(E39),E39,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J39),J39,""),IF('Status'!$B$14=2,IF(ISNUMBER(K39),K39,""),IF('Status'!$B$14=3,IF(ISNUMBER(L39),L39,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="6"/>
@@ -2927,6 +3089,9 @@
       <x:c r="S40" s="2" t="str">
         <x:f>IF(COUNTA(A40)=0,"",IF(COUNTIFS($A$6:$A$165,A40)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T40" s="23" t="str">
+        <x:f>IF(COUNTA($A40)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C40),C40,""),IF('Status'!$B$14=2,IF(ISNUMBER(D40),D40,""),IF('Status'!$B$14=3,IF(ISNUMBER(E40),E40,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J40),J40,""),IF('Status'!$B$14=2,IF(ISNUMBER(K40),K40,""),IF('Status'!$B$14=3,IF(ISNUMBER(L40),L40,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="6"/>
@@ -2982,6 +3147,9 @@
       <x:c r="S41" s="2" t="str">
         <x:f>IF(COUNTA(A41)=0,"",IF(COUNTIFS($A$6:$A$165,A41)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T41" s="23" t="str">
+        <x:f>IF(COUNTA($A41)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C41),C41,""),IF('Status'!$B$14=2,IF(ISNUMBER(D41),D41,""),IF('Status'!$B$14=3,IF(ISNUMBER(E41),E41,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J41),J41,""),IF('Status'!$B$14=2,IF(ISNUMBER(K41),K41,""),IF('Status'!$B$14=3,IF(ISNUMBER(L41),L41,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="6"/>
@@ -3037,6 +3205,9 @@
       <x:c r="S42" s="2" t="str">
         <x:f>IF(COUNTA(A42)=0,"",IF(COUNTIFS($A$6:$A$165,A42)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T42" s="23" t="str">
+        <x:f>IF(COUNTA($A42)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C42),C42,""),IF('Status'!$B$14=2,IF(ISNUMBER(D42),D42,""),IF('Status'!$B$14=3,IF(ISNUMBER(E42),E42,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J42),J42,""),IF('Status'!$B$14=2,IF(ISNUMBER(K42),K42,""),IF('Status'!$B$14=3,IF(ISNUMBER(L42),L42,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="6"/>
@@ -3092,6 +3263,9 @@
       <x:c r="S43" s="2" t="str">
         <x:f>IF(COUNTA(A43)=0,"",IF(COUNTIFS($A$6:$A$165,A43)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T43" s="23" t="str">
+        <x:f>IF(COUNTA($A43)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C43),C43,""),IF('Status'!$B$14=2,IF(ISNUMBER(D43),D43,""),IF('Status'!$B$14=3,IF(ISNUMBER(E43),E43,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J43),J43,""),IF('Status'!$B$14=2,IF(ISNUMBER(K43),K43,""),IF('Status'!$B$14=3,IF(ISNUMBER(L43),L43,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="6"/>
@@ -3147,6 +3321,9 @@
       <x:c r="S44" s="2" t="str">
         <x:f>IF(COUNTA(A44)=0,"",IF(COUNTIFS($A$6:$A$165,A44)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T44" s="23" t="str">
+        <x:f>IF(COUNTA($A44)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C44),C44,""),IF('Status'!$B$14=2,IF(ISNUMBER(D44),D44,""),IF('Status'!$B$14=3,IF(ISNUMBER(E44),E44,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J44),J44,""),IF('Status'!$B$14=2,IF(ISNUMBER(K44),K44,""),IF('Status'!$B$14=3,IF(ISNUMBER(L44),L44,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="6"/>
@@ -3202,6 +3379,9 @@
       <x:c r="S45" s="2" t="str">
         <x:f>IF(COUNTA(A45)=0,"",IF(COUNTIFS($A$6:$A$165,A45)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T45" s="23" t="str">
+        <x:f>IF(COUNTA($A45)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C45),C45,""),IF('Status'!$B$14=2,IF(ISNUMBER(D45),D45,""),IF('Status'!$B$14=3,IF(ISNUMBER(E45),E45,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J45),J45,""),IF('Status'!$B$14=2,IF(ISNUMBER(K45),K45,""),IF('Status'!$B$14=3,IF(ISNUMBER(L45),L45,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="6"/>
@@ -3257,6 +3437,9 @@
       <x:c r="S46" s="2" t="str">
         <x:f>IF(COUNTA(A46)=0,"",IF(COUNTIFS($A$6:$A$165,A46)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T46" s="23" t="str">
+        <x:f>IF(COUNTA($A46)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C46),C46,""),IF('Status'!$B$14=2,IF(ISNUMBER(D46),D46,""),IF('Status'!$B$14=3,IF(ISNUMBER(E46),E46,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J46),J46,""),IF('Status'!$B$14=2,IF(ISNUMBER(K46),K46,""),IF('Status'!$B$14=3,IF(ISNUMBER(L46),L46,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="6"/>
@@ -3312,6 +3495,9 @@
       <x:c r="S47" s="2" t="str">
         <x:f>IF(COUNTA(A47)=0,"",IF(COUNTIFS($A$6:$A$165,A47)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T47" s="23" t="str">
+        <x:f>IF(COUNTA($A47)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C47),C47,""),IF('Status'!$B$14=2,IF(ISNUMBER(D47),D47,""),IF('Status'!$B$14=3,IF(ISNUMBER(E47),E47,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J47),J47,""),IF('Status'!$B$14=2,IF(ISNUMBER(K47),K47,""),IF('Status'!$B$14=3,IF(ISNUMBER(L47),L47,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="6"/>
@@ -3367,6 +3553,9 @@
       <x:c r="S48" s="2" t="str">
         <x:f>IF(COUNTA(A48)=0,"",IF(COUNTIFS($A$6:$A$165,A48)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T48" s="23" t="str">
+        <x:f>IF(COUNTA($A48)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C48),C48,""),IF('Status'!$B$14=2,IF(ISNUMBER(D48),D48,""),IF('Status'!$B$14=3,IF(ISNUMBER(E48),E48,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J48),J48,""),IF('Status'!$B$14=2,IF(ISNUMBER(K48),K48,""),IF('Status'!$B$14=3,IF(ISNUMBER(L48),L48,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="6"/>
@@ -3422,6 +3611,9 @@
       <x:c r="S49" s="2" t="str">
         <x:f>IF(COUNTA(A49)=0,"",IF(COUNTIFS($A$6:$A$165,A49)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T49" s="23" t="str">
+        <x:f>IF(COUNTA($A49)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C49),C49,""),IF('Status'!$B$14=2,IF(ISNUMBER(D49),D49,""),IF('Status'!$B$14=3,IF(ISNUMBER(E49),E49,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J49),J49,""),IF('Status'!$B$14=2,IF(ISNUMBER(K49),K49,""),IF('Status'!$B$14=3,IF(ISNUMBER(L49),L49,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="6"/>
@@ -3477,6 +3669,9 @@
       <x:c r="S50" s="2" t="str">
         <x:f>IF(COUNTA(A50)=0,"",IF(COUNTIFS($A$6:$A$165,A50)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T50" s="23" t="str">
+        <x:f>IF(COUNTA($A50)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C50),C50,""),IF('Status'!$B$14=2,IF(ISNUMBER(D50),D50,""),IF('Status'!$B$14=3,IF(ISNUMBER(E50),E50,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J50),J50,""),IF('Status'!$B$14=2,IF(ISNUMBER(K50),K50,""),IF('Status'!$B$14=3,IF(ISNUMBER(L50),L50,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="6"/>
@@ -3532,6 +3727,9 @@
       <x:c r="S51" s="2" t="str">
         <x:f>IF(COUNTA(A51)=0,"",IF(COUNTIFS($A$6:$A$165,A51)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T51" s="23" t="str">
+        <x:f>IF(COUNTA($A51)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C51),C51,""),IF('Status'!$B$14=2,IF(ISNUMBER(D51),D51,""),IF('Status'!$B$14=3,IF(ISNUMBER(E51),E51,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J51),J51,""),IF('Status'!$B$14=2,IF(ISNUMBER(K51),K51,""),IF('Status'!$B$14=3,IF(ISNUMBER(L51),L51,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="6"/>
@@ -3587,6 +3785,9 @@
       <x:c r="S52" s="2" t="str">
         <x:f>IF(COUNTA(A52)=0,"",IF(COUNTIFS($A$6:$A$165,A52)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T52" s="23" t="str">
+        <x:f>IF(COUNTA($A52)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C52),C52,""),IF('Status'!$B$14=2,IF(ISNUMBER(D52),D52,""),IF('Status'!$B$14=3,IF(ISNUMBER(E52),E52,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J52),J52,""),IF('Status'!$B$14=2,IF(ISNUMBER(K52),K52,""),IF('Status'!$B$14=3,IF(ISNUMBER(L52),L52,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="6"/>
@@ -3642,6 +3843,9 @@
       <x:c r="S53" s="2" t="str">
         <x:f>IF(COUNTA(A53)=0,"",IF(COUNTIFS($A$6:$A$165,A53)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T53" s="23" t="str">
+        <x:f>IF(COUNTA($A53)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C53),C53,""),IF('Status'!$B$14=2,IF(ISNUMBER(D53),D53,""),IF('Status'!$B$14=3,IF(ISNUMBER(E53),E53,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J53),J53,""),IF('Status'!$B$14=2,IF(ISNUMBER(K53),K53,""),IF('Status'!$B$14=3,IF(ISNUMBER(L53),L53,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="6"/>
@@ -3697,6 +3901,9 @@
       <x:c r="S54" s="2" t="str">
         <x:f>IF(COUNTA(A54)=0,"",IF(COUNTIFS($A$6:$A$165,A54)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T54" s="23" t="str">
+        <x:f>IF(COUNTA($A54)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C54),C54,""),IF('Status'!$B$14=2,IF(ISNUMBER(D54),D54,""),IF('Status'!$B$14=3,IF(ISNUMBER(E54),E54,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J54),J54,""),IF('Status'!$B$14=2,IF(ISNUMBER(K54),K54,""),IF('Status'!$B$14=3,IF(ISNUMBER(L54),L54,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="6"/>
@@ -3752,6 +3959,9 @@
       <x:c r="S55" s="2" t="str">
         <x:f>IF(COUNTA(A55)=0,"",IF(COUNTIFS($A$6:$A$165,A55)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T55" s="23" t="str">
+        <x:f>IF(COUNTA($A55)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C55),C55,""),IF('Status'!$B$14=2,IF(ISNUMBER(D55),D55,""),IF('Status'!$B$14=3,IF(ISNUMBER(E55),E55,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J55),J55,""),IF('Status'!$B$14=2,IF(ISNUMBER(K55),K55,""),IF('Status'!$B$14=3,IF(ISNUMBER(L55),L55,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="6"/>
@@ -3807,6 +4017,9 @@
       <x:c r="S56" s="2" t="str">
         <x:f>IF(COUNTA(A56)=0,"",IF(COUNTIFS($A$6:$A$165,A56)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T56" s="23" t="str">
+        <x:f>IF(COUNTA($A56)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C56),C56,""),IF('Status'!$B$14=2,IF(ISNUMBER(D56),D56,""),IF('Status'!$B$14=3,IF(ISNUMBER(E56),E56,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J56),J56,""),IF('Status'!$B$14=2,IF(ISNUMBER(K56),K56,""),IF('Status'!$B$14=3,IF(ISNUMBER(L56),L56,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="6"/>
@@ -3862,6 +4075,9 @@
       <x:c r="S57" s="2" t="str">
         <x:f>IF(COUNTA(A57)=0,"",IF(COUNTIFS($A$6:$A$165,A57)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T57" s="23" t="str">
+        <x:f>IF(COUNTA($A57)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C57),C57,""),IF('Status'!$B$14=2,IF(ISNUMBER(D57),D57,""),IF('Status'!$B$14=3,IF(ISNUMBER(E57),E57,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J57),J57,""),IF('Status'!$B$14=2,IF(ISNUMBER(K57),K57,""),IF('Status'!$B$14=3,IF(ISNUMBER(L57),L57,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="6"/>
@@ -3917,6 +4133,9 @@
       <x:c r="S58" s="2" t="str">
         <x:f>IF(COUNTA(A58)=0,"",IF(COUNTIFS($A$6:$A$165,A58)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T58" s="23" t="str">
+        <x:f>IF(COUNTA($A58)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C58),C58,""),IF('Status'!$B$14=2,IF(ISNUMBER(D58),D58,""),IF('Status'!$B$14=3,IF(ISNUMBER(E58),E58,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J58),J58,""),IF('Status'!$B$14=2,IF(ISNUMBER(K58),K58,""),IF('Status'!$B$14=3,IF(ISNUMBER(L58),L58,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="6"/>
@@ -3972,6 +4191,9 @@
       <x:c r="S59" s="2" t="str">
         <x:f>IF(COUNTA(A59)=0,"",IF(COUNTIFS($A$6:$A$165,A59)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T59" s="23" t="str">
+        <x:f>IF(COUNTA($A59)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C59),C59,""),IF('Status'!$B$14=2,IF(ISNUMBER(D59),D59,""),IF('Status'!$B$14=3,IF(ISNUMBER(E59),E59,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J59),J59,""),IF('Status'!$B$14=2,IF(ISNUMBER(K59),K59,""),IF('Status'!$B$14=3,IF(ISNUMBER(L59),L59,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="6"/>
@@ -4027,6 +4249,9 @@
       <x:c r="S60" s="2" t="str">
         <x:f>IF(COUNTA(A60)=0,"",IF(COUNTIFS($A$6:$A$165,A60)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T60" s="23" t="str">
+        <x:f>IF(COUNTA($A60)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C60),C60,""),IF('Status'!$B$14=2,IF(ISNUMBER(D60),D60,""),IF('Status'!$B$14=3,IF(ISNUMBER(E60),E60,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J60),J60,""),IF('Status'!$B$14=2,IF(ISNUMBER(K60),K60,""),IF('Status'!$B$14=3,IF(ISNUMBER(L60),L60,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="6"/>
@@ -4082,6 +4307,9 @@
       <x:c r="S61" s="2" t="str">
         <x:f>IF(COUNTA(A61)=0,"",IF(COUNTIFS($A$6:$A$165,A61)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T61" s="23" t="str">
+        <x:f>IF(COUNTA($A61)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C61),C61,""),IF('Status'!$B$14=2,IF(ISNUMBER(D61),D61,""),IF('Status'!$B$14=3,IF(ISNUMBER(E61),E61,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J61),J61,""),IF('Status'!$B$14=2,IF(ISNUMBER(K61),K61,""),IF('Status'!$B$14=3,IF(ISNUMBER(L61),L61,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="6"/>
@@ -4137,6 +4365,9 @@
       <x:c r="S62" s="2" t="str">
         <x:f>IF(COUNTA(A62)=0,"",IF(COUNTIFS($A$6:$A$165,A62)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T62" s="23" t="str">
+        <x:f>IF(COUNTA($A62)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C62),C62,""),IF('Status'!$B$14=2,IF(ISNUMBER(D62),D62,""),IF('Status'!$B$14=3,IF(ISNUMBER(E62),E62,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J62),J62,""),IF('Status'!$B$14=2,IF(ISNUMBER(K62),K62,""),IF('Status'!$B$14=3,IF(ISNUMBER(L62),L62,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="6"/>
@@ -4192,6 +4423,9 @@
       <x:c r="S63" s="2" t="str">
         <x:f>IF(COUNTA(A63)=0,"",IF(COUNTIFS($A$6:$A$165,A63)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T63" s="23" t="str">
+        <x:f>IF(COUNTA($A63)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C63),C63,""),IF('Status'!$B$14=2,IF(ISNUMBER(D63),D63,""),IF('Status'!$B$14=3,IF(ISNUMBER(E63),E63,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J63),J63,""),IF('Status'!$B$14=2,IF(ISNUMBER(K63),K63,""),IF('Status'!$B$14=3,IF(ISNUMBER(L63),L63,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="6"/>
@@ -4247,6 +4481,9 @@
       <x:c r="S64" s="2" t="str">
         <x:f>IF(COUNTA(A64)=0,"",IF(COUNTIFS($A$6:$A$165,A64)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T64" s="23" t="str">
+        <x:f>IF(COUNTA($A64)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C64),C64,""),IF('Status'!$B$14=2,IF(ISNUMBER(D64),D64,""),IF('Status'!$B$14=3,IF(ISNUMBER(E64),E64,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J64),J64,""),IF('Status'!$B$14=2,IF(ISNUMBER(K64),K64,""),IF('Status'!$B$14=3,IF(ISNUMBER(L64),L64,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="6"/>
@@ -4302,6 +4539,9 @@
       <x:c r="S65" s="2" t="str">
         <x:f>IF(COUNTA(A65)=0,"",IF(COUNTIFS($A$6:$A$165,A65)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T65" s="23" t="str">
+        <x:f>IF(COUNTA($A65)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C65),C65,""),IF('Status'!$B$14=2,IF(ISNUMBER(D65),D65,""),IF('Status'!$B$14=3,IF(ISNUMBER(E65),E65,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J65),J65,""),IF('Status'!$B$14=2,IF(ISNUMBER(K65),K65,""),IF('Status'!$B$14=3,IF(ISNUMBER(L65),L65,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="6"/>
@@ -4357,6 +4597,9 @@
       <x:c r="S66" s="2" t="str">
         <x:f>IF(COUNTA(A66)=0,"",IF(COUNTIFS($A$6:$A$165,A66)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T66" s="23" t="str">
+        <x:f>IF(COUNTA($A66)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C66),C66,""),IF('Status'!$B$14=2,IF(ISNUMBER(D66),D66,""),IF('Status'!$B$14=3,IF(ISNUMBER(E66),E66,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J66),J66,""),IF('Status'!$B$14=2,IF(ISNUMBER(K66),K66,""),IF('Status'!$B$14=3,IF(ISNUMBER(L66),L66,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="6"/>
@@ -4412,6 +4655,9 @@
       <x:c r="S67" s="2" t="str">
         <x:f>IF(COUNTA(A67)=0,"",IF(COUNTIFS($A$6:$A$165,A67)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T67" s="23" t="str">
+        <x:f>IF(COUNTA($A67)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C67),C67,""),IF('Status'!$B$14=2,IF(ISNUMBER(D67),D67,""),IF('Status'!$B$14=3,IF(ISNUMBER(E67),E67,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J67),J67,""),IF('Status'!$B$14=2,IF(ISNUMBER(K67),K67,""),IF('Status'!$B$14=3,IF(ISNUMBER(L67),L67,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="6"/>
@@ -4467,6 +4713,9 @@
       <x:c r="S68" s="2" t="str">
         <x:f>IF(COUNTA(A68)=0,"",IF(COUNTIFS($A$6:$A$165,A68)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T68" s="23" t="str">
+        <x:f>IF(COUNTA($A68)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C68),C68,""),IF('Status'!$B$14=2,IF(ISNUMBER(D68),D68,""),IF('Status'!$B$14=3,IF(ISNUMBER(E68),E68,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J68),J68,""),IF('Status'!$B$14=2,IF(ISNUMBER(K68),K68,""),IF('Status'!$B$14=3,IF(ISNUMBER(L68),L68,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="6"/>
@@ -4522,6 +4771,9 @@
       <x:c r="S69" s="2" t="str">
         <x:f>IF(COUNTA(A69)=0,"",IF(COUNTIFS($A$6:$A$165,A69)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T69" s="23" t="str">
+        <x:f>IF(COUNTA($A69)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C69),C69,""),IF('Status'!$B$14=2,IF(ISNUMBER(D69),D69,""),IF('Status'!$B$14=3,IF(ISNUMBER(E69),E69,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J69),J69,""),IF('Status'!$B$14=2,IF(ISNUMBER(K69),K69,""),IF('Status'!$B$14=3,IF(ISNUMBER(L69),L69,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="6"/>
@@ -4577,6 +4829,9 @@
       <x:c r="S70" s="2" t="str">
         <x:f>IF(COUNTA(A70)=0,"",IF(COUNTIFS($A$6:$A$165,A70)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T70" s="23" t="str">
+        <x:f>IF(COUNTA($A70)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C70),C70,""),IF('Status'!$B$14=2,IF(ISNUMBER(D70),D70,""),IF('Status'!$B$14=3,IF(ISNUMBER(E70),E70,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J70),J70,""),IF('Status'!$B$14=2,IF(ISNUMBER(K70),K70,""),IF('Status'!$B$14=3,IF(ISNUMBER(L70),L70,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="6"/>
@@ -4632,6 +4887,9 @@
       <x:c r="S71" s="2" t="str">
         <x:f>IF(COUNTA(A71)=0,"",IF(COUNTIFS($A$6:$A$165,A71)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T71" s="23" t="str">
+        <x:f>IF(COUNTA($A71)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C71),C71,""),IF('Status'!$B$14=2,IF(ISNUMBER(D71),D71,""),IF('Status'!$B$14=3,IF(ISNUMBER(E71),E71,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J71),J71,""),IF('Status'!$B$14=2,IF(ISNUMBER(K71),K71,""),IF('Status'!$B$14=3,IF(ISNUMBER(L71),L71,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="6"/>
@@ -4687,6 +4945,9 @@
       <x:c r="S72" s="2" t="str">
         <x:f>IF(COUNTA(A72)=0,"",IF(COUNTIFS($A$6:$A$165,A72)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T72" s="23" t="str">
+        <x:f>IF(COUNTA($A72)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C72),C72,""),IF('Status'!$B$14=2,IF(ISNUMBER(D72),D72,""),IF('Status'!$B$14=3,IF(ISNUMBER(E72),E72,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J72),J72,""),IF('Status'!$B$14=2,IF(ISNUMBER(K72),K72,""),IF('Status'!$B$14=3,IF(ISNUMBER(L72),L72,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="6"/>
@@ -4742,6 +5003,9 @@
       <x:c r="S73" s="2" t="str">
         <x:f>IF(COUNTA(A73)=0,"",IF(COUNTIFS($A$6:$A$165,A73)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T73" s="23" t="str">
+        <x:f>IF(COUNTA($A73)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C73),C73,""),IF('Status'!$B$14=2,IF(ISNUMBER(D73),D73,""),IF('Status'!$B$14=3,IF(ISNUMBER(E73),E73,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J73),J73,""),IF('Status'!$B$14=2,IF(ISNUMBER(K73),K73,""),IF('Status'!$B$14=3,IF(ISNUMBER(L73),L73,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="6"/>
@@ -4797,6 +5061,9 @@
       <x:c r="S74" s="2" t="str">
         <x:f>IF(COUNTA(A74)=0,"",IF(COUNTIFS($A$6:$A$165,A74)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T74" s="23" t="str">
+        <x:f>IF(COUNTA($A74)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C74),C74,""),IF('Status'!$B$14=2,IF(ISNUMBER(D74),D74,""),IF('Status'!$B$14=3,IF(ISNUMBER(E74),E74,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J74),J74,""),IF('Status'!$B$14=2,IF(ISNUMBER(K74),K74,""),IF('Status'!$B$14=3,IF(ISNUMBER(L74),L74,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="6"/>
@@ -4852,6 +5119,9 @@
       <x:c r="S75" s="2" t="str">
         <x:f>IF(COUNTA(A75)=0,"",IF(COUNTIFS($A$6:$A$165,A75)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T75" s="23" t="str">
+        <x:f>IF(COUNTA($A75)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C75),C75,""),IF('Status'!$B$14=2,IF(ISNUMBER(D75),D75,""),IF('Status'!$B$14=3,IF(ISNUMBER(E75),E75,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J75),J75,""),IF('Status'!$B$14=2,IF(ISNUMBER(K75),K75,""),IF('Status'!$B$14=3,IF(ISNUMBER(L75),L75,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="6"/>
@@ -4907,6 +5177,9 @@
       <x:c r="S76" s="2" t="str">
         <x:f>IF(COUNTA(A76)=0,"",IF(COUNTIFS($A$6:$A$165,A76)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T76" s="23" t="str">
+        <x:f>IF(COUNTA($A76)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C76),C76,""),IF('Status'!$B$14=2,IF(ISNUMBER(D76),D76,""),IF('Status'!$B$14=3,IF(ISNUMBER(E76),E76,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J76),J76,""),IF('Status'!$B$14=2,IF(ISNUMBER(K76),K76,""),IF('Status'!$B$14=3,IF(ISNUMBER(L76),L76,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="6"/>
@@ -4962,6 +5235,9 @@
       <x:c r="S77" s="2" t="str">
         <x:f>IF(COUNTA(A77)=0,"",IF(COUNTIFS($A$6:$A$165,A77)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T77" s="23" t="str">
+        <x:f>IF(COUNTA($A77)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C77),C77,""),IF('Status'!$B$14=2,IF(ISNUMBER(D77),D77,""),IF('Status'!$B$14=3,IF(ISNUMBER(E77),E77,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J77),J77,""),IF('Status'!$B$14=2,IF(ISNUMBER(K77),K77,""),IF('Status'!$B$14=3,IF(ISNUMBER(L77),L77,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="6"/>
@@ -5017,6 +5293,9 @@
       <x:c r="S78" s="2" t="str">
         <x:f>IF(COUNTA(A78)=0,"",IF(COUNTIFS($A$6:$A$165,A78)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T78" s="23" t="str">
+        <x:f>IF(COUNTA($A78)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C78),C78,""),IF('Status'!$B$14=2,IF(ISNUMBER(D78),D78,""),IF('Status'!$B$14=3,IF(ISNUMBER(E78),E78,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J78),J78,""),IF('Status'!$B$14=2,IF(ISNUMBER(K78),K78,""),IF('Status'!$B$14=3,IF(ISNUMBER(L78),L78,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="6"/>
@@ -5072,6 +5351,9 @@
       <x:c r="S79" s="2" t="str">
         <x:f>IF(COUNTA(A79)=0,"",IF(COUNTIFS($A$6:$A$165,A79)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T79" s="23" t="str">
+        <x:f>IF(COUNTA($A79)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C79),C79,""),IF('Status'!$B$14=2,IF(ISNUMBER(D79),D79,""),IF('Status'!$B$14=3,IF(ISNUMBER(E79),E79,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J79),J79,""),IF('Status'!$B$14=2,IF(ISNUMBER(K79),K79,""),IF('Status'!$B$14=3,IF(ISNUMBER(L79),L79,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="6"/>
@@ -5127,6 +5409,9 @@
       <x:c r="S80" s="2" t="str">
         <x:f>IF(COUNTA(A80)=0,"",IF(COUNTIFS($A$6:$A$165,A80)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T80" s="23" t="str">
+        <x:f>IF(COUNTA($A80)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C80),C80,""),IF('Status'!$B$14=2,IF(ISNUMBER(D80),D80,""),IF('Status'!$B$14=3,IF(ISNUMBER(E80),E80,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J80),J80,""),IF('Status'!$B$14=2,IF(ISNUMBER(K80),K80,""),IF('Status'!$B$14=3,IF(ISNUMBER(L80),L80,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="6"/>
@@ -5182,6 +5467,9 @@
       <x:c r="S81" s="2" t="str">
         <x:f>IF(COUNTA(A81)=0,"",IF(COUNTIFS($A$6:$A$165,A81)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T81" s="23" t="str">
+        <x:f>IF(COUNTA($A81)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C81),C81,""),IF('Status'!$B$14=2,IF(ISNUMBER(D81),D81,""),IF('Status'!$B$14=3,IF(ISNUMBER(E81),E81,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J81),J81,""),IF('Status'!$B$14=2,IF(ISNUMBER(K81),K81,""),IF('Status'!$B$14=3,IF(ISNUMBER(L81),L81,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="6"/>
@@ -5237,6 +5525,9 @@
       <x:c r="S82" s="2" t="str">
         <x:f>IF(COUNTA(A82)=0,"",IF(COUNTIFS($A$6:$A$165,A82)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T82" s="23" t="str">
+        <x:f>IF(COUNTA($A82)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C82),C82,""),IF('Status'!$B$14=2,IF(ISNUMBER(D82),D82,""),IF('Status'!$B$14=3,IF(ISNUMBER(E82),E82,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J82),J82,""),IF('Status'!$B$14=2,IF(ISNUMBER(K82),K82,""),IF('Status'!$B$14=3,IF(ISNUMBER(L82),L82,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="6"/>
@@ -5292,6 +5583,9 @@
       <x:c r="S83" s="2" t="str">
         <x:f>IF(COUNTA(A83)=0,"",IF(COUNTIFS($A$6:$A$165,A83)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T83" s="23" t="str">
+        <x:f>IF(COUNTA($A83)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C83),C83,""),IF('Status'!$B$14=2,IF(ISNUMBER(D83),D83,""),IF('Status'!$B$14=3,IF(ISNUMBER(E83),E83,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J83),J83,""),IF('Status'!$B$14=2,IF(ISNUMBER(K83),K83,""),IF('Status'!$B$14=3,IF(ISNUMBER(L83),L83,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="6"/>
@@ -5347,6 +5641,9 @@
       <x:c r="S84" s="2" t="str">
         <x:f>IF(COUNTA(A84)=0,"",IF(COUNTIFS($A$6:$A$165,A84)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T84" s="23" t="str">
+        <x:f>IF(COUNTA($A84)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C84),C84,""),IF('Status'!$B$14=2,IF(ISNUMBER(D84),D84,""),IF('Status'!$B$14=3,IF(ISNUMBER(E84),E84,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J84),J84,""),IF('Status'!$B$14=2,IF(ISNUMBER(K84),K84,""),IF('Status'!$B$14=3,IF(ISNUMBER(L84),L84,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="6"/>
@@ -5402,6 +5699,9 @@
       <x:c r="S85" s="2" t="str">
         <x:f>IF(COUNTA(A85)=0,"",IF(COUNTIFS($A$6:$A$165,A85)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T85" s="23" t="str">
+        <x:f>IF(COUNTA($A85)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C85),C85,""),IF('Status'!$B$14=2,IF(ISNUMBER(D85),D85,""),IF('Status'!$B$14=3,IF(ISNUMBER(E85),E85,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J85),J85,""),IF('Status'!$B$14=2,IF(ISNUMBER(K85),K85,""),IF('Status'!$B$14=3,IF(ISNUMBER(L85),L85,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="6"/>
@@ -5457,6 +5757,9 @@
       <x:c r="S86" s="2" t="str">
         <x:f>IF(COUNTA(A86)=0,"",IF(COUNTIFS($A$6:$A$165,A86)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T86" s="23" t="str">
+        <x:f>IF(COUNTA($A86)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C86),C86,""),IF('Status'!$B$14=2,IF(ISNUMBER(D86),D86,""),IF('Status'!$B$14=3,IF(ISNUMBER(E86),E86,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J86),J86,""),IF('Status'!$B$14=2,IF(ISNUMBER(K86),K86,""),IF('Status'!$B$14=3,IF(ISNUMBER(L86),L86,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="6"/>
@@ -5512,6 +5815,9 @@
       <x:c r="S87" s="2" t="str">
         <x:f>IF(COUNTA(A87)=0,"",IF(COUNTIFS($A$6:$A$165,A87)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T87" s="23" t="str">
+        <x:f>IF(COUNTA($A87)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C87),C87,""),IF('Status'!$B$14=2,IF(ISNUMBER(D87),D87,""),IF('Status'!$B$14=3,IF(ISNUMBER(E87),E87,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J87),J87,""),IF('Status'!$B$14=2,IF(ISNUMBER(K87),K87,""),IF('Status'!$B$14=3,IF(ISNUMBER(L87),L87,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="6"/>
@@ -5567,6 +5873,9 @@
       <x:c r="S88" s="2" t="str">
         <x:f>IF(COUNTA(A88)=0,"",IF(COUNTIFS($A$6:$A$165,A88)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T88" s="23" t="str">
+        <x:f>IF(COUNTA($A88)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C88),C88,""),IF('Status'!$B$14=2,IF(ISNUMBER(D88),D88,""),IF('Status'!$B$14=3,IF(ISNUMBER(E88),E88,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J88),J88,""),IF('Status'!$B$14=2,IF(ISNUMBER(K88),K88,""),IF('Status'!$B$14=3,IF(ISNUMBER(L88),L88,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="6"/>
@@ -5622,6 +5931,9 @@
       <x:c r="S89" s="2" t="str">
         <x:f>IF(COUNTA(A89)=0,"",IF(COUNTIFS($A$6:$A$165,A89)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T89" s="23" t="str">
+        <x:f>IF(COUNTA($A89)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C89),C89,""),IF('Status'!$B$14=2,IF(ISNUMBER(D89),D89,""),IF('Status'!$B$14=3,IF(ISNUMBER(E89),E89,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J89),J89,""),IF('Status'!$B$14=2,IF(ISNUMBER(K89),K89,""),IF('Status'!$B$14=3,IF(ISNUMBER(L89),L89,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="6"/>
@@ -5677,6 +5989,9 @@
       <x:c r="S90" s="2" t="str">
         <x:f>IF(COUNTA(A90)=0,"",IF(COUNTIFS($A$6:$A$165,A90)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T90" s="23" t="str">
+        <x:f>IF(COUNTA($A90)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C90),C90,""),IF('Status'!$B$14=2,IF(ISNUMBER(D90),D90,""),IF('Status'!$B$14=3,IF(ISNUMBER(E90),E90,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J90),J90,""),IF('Status'!$B$14=2,IF(ISNUMBER(K90),K90,""),IF('Status'!$B$14=3,IF(ISNUMBER(L90),L90,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="6"/>
@@ -5732,6 +6047,9 @@
       <x:c r="S91" s="2" t="str">
         <x:f>IF(COUNTA(A91)=0,"",IF(COUNTIFS($A$6:$A$165,A91)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T91" s="23" t="str">
+        <x:f>IF(COUNTA($A91)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C91),C91,""),IF('Status'!$B$14=2,IF(ISNUMBER(D91),D91,""),IF('Status'!$B$14=3,IF(ISNUMBER(E91),E91,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J91),J91,""),IF('Status'!$B$14=2,IF(ISNUMBER(K91),K91,""),IF('Status'!$B$14=3,IF(ISNUMBER(L91),L91,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="6"/>
@@ -5787,6 +6105,9 @@
       <x:c r="S92" s="2" t="str">
         <x:f>IF(COUNTA(A92)=0,"",IF(COUNTIFS($A$6:$A$165,A92)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T92" s="23" t="str">
+        <x:f>IF(COUNTA($A92)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C92),C92,""),IF('Status'!$B$14=2,IF(ISNUMBER(D92),D92,""),IF('Status'!$B$14=3,IF(ISNUMBER(E92),E92,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J92),J92,""),IF('Status'!$B$14=2,IF(ISNUMBER(K92),K92,""),IF('Status'!$B$14=3,IF(ISNUMBER(L92),L92,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="6"/>
@@ -5842,6 +6163,9 @@
       <x:c r="S93" s="2" t="str">
         <x:f>IF(COUNTA(A93)=0,"",IF(COUNTIFS($A$6:$A$165,A93)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T93" s="23" t="str">
+        <x:f>IF(COUNTA($A93)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C93),C93,""),IF('Status'!$B$14=2,IF(ISNUMBER(D93),D93,""),IF('Status'!$B$14=3,IF(ISNUMBER(E93),E93,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J93),J93,""),IF('Status'!$B$14=2,IF(ISNUMBER(K93),K93,""),IF('Status'!$B$14=3,IF(ISNUMBER(L93),L93,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="6"/>
@@ -5897,6 +6221,9 @@
       <x:c r="S94" s="2" t="str">
         <x:f>IF(COUNTA(A94)=0,"",IF(COUNTIFS($A$6:$A$165,A94)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T94" s="23" t="str">
+        <x:f>IF(COUNTA($A94)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C94),C94,""),IF('Status'!$B$14=2,IF(ISNUMBER(D94),D94,""),IF('Status'!$B$14=3,IF(ISNUMBER(E94),E94,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J94),J94,""),IF('Status'!$B$14=2,IF(ISNUMBER(K94),K94,""),IF('Status'!$B$14=3,IF(ISNUMBER(L94),L94,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="6"/>
@@ -5952,6 +6279,9 @@
       <x:c r="S95" s="2" t="str">
         <x:f>IF(COUNTA(A95)=0,"",IF(COUNTIFS($A$6:$A$165,A95)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T95" s="23" t="str">
+        <x:f>IF(COUNTA($A95)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C95),C95,""),IF('Status'!$B$14=2,IF(ISNUMBER(D95),D95,""),IF('Status'!$B$14=3,IF(ISNUMBER(E95),E95,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J95),J95,""),IF('Status'!$B$14=2,IF(ISNUMBER(K95),K95,""),IF('Status'!$B$14=3,IF(ISNUMBER(L95),L95,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="6"/>
@@ -6007,6 +6337,9 @@
       <x:c r="S96" s="2" t="str">
         <x:f>IF(COUNTA(A96)=0,"",IF(COUNTIFS($A$6:$A$165,A96)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T96" s="23" t="str">
+        <x:f>IF(COUNTA($A96)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C96),C96,""),IF('Status'!$B$14=2,IF(ISNUMBER(D96),D96,""),IF('Status'!$B$14=3,IF(ISNUMBER(E96),E96,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J96),J96,""),IF('Status'!$B$14=2,IF(ISNUMBER(K96),K96,""),IF('Status'!$B$14=3,IF(ISNUMBER(L96),L96,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="6"/>
@@ -6062,6 +6395,9 @@
       <x:c r="S97" s="2" t="str">
         <x:f>IF(COUNTA(A97)=0,"",IF(COUNTIFS($A$6:$A$165,A97)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T97" s="23" t="str">
+        <x:f>IF(COUNTA($A97)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C97),C97,""),IF('Status'!$B$14=2,IF(ISNUMBER(D97),D97,""),IF('Status'!$B$14=3,IF(ISNUMBER(E97),E97,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J97),J97,""),IF('Status'!$B$14=2,IF(ISNUMBER(K97),K97,""),IF('Status'!$B$14=3,IF(ISNUMBER(L97),L97,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="6"/>
@@ -6117,6 +6453,9 @@
       <x:c r="S98" s="2" t="str">
         <x:f>IF(COUNTA(A98)=0,"",IF(COUNTIFS($A$6:$A$165,A98)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T98" s="23" t="str">
+        <x:f>IF(COUNTA($A98)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C98),C98,""),IF('Status'!$B$14=2,IF(ISNUMBER(D98),D98,""),IF('Status'!$B$14=3,IF(ISNUMBER(E98),E98,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J98),J98,""),IF('Status'!$B$14=2,IF(ISNUMBER(K98),K98,""),IF('Status'!$B$14=3,IF(ISNUMBER(L98),L98,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="6"/>
@@ -6172,6 +6511,9 @@
       <x:c r="S99" s="2" t="str">
         <x:f>IF(COUNTA(A99)=0,"",IF(COUNTIFS($A$6:$A$165,A99)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T99" s="23" t="str">
+        <x:f>IF(COUNTA($A99)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C99),C99,""),IF('Status'!$B$14=2,IF(ISNUMBER(D99),D99,""),IF('Status'!$B$14=3,IF(ISNUMBER(E99),E99,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J99),J99,""),IF('Status'!$B$14=2,IF(ISNUMBER(K99),K99,""),IF('Status'!$B$14=3,IF(ISNUMBER(L99),L99,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="6"/>
@@ -6227,6 +6569,9 @@
       <x:c r="S100" s="2" t="str">
         <x:f>IF(COUNTA(A100)=0,"",IF(COUNTIFS($A$6:$A$165,A100)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T100" s="23" t="str">
+        <x:f>IF(COUNTA($A100)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C100),C100,""),IF('Status'!$B$14=2,IF(ISNUMBER(D100),D100,""),IF('Status'!$B$14=3,IF(ISNUMBER(E100),E100,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J100),J100,""),IF('Status'!$B$14=2,IF(ISNUMBER(K100),K100,""),IF('Status'!$B$14=3,IF(ISNUMBER(L100),L100,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="6"/>
@@ -6282,6 +6627,9 @@
       <x:c r="S101" s="2" t="str">
         <x:f>IF(COUNTA(A101)=0,"",IF(COUNTIFS($A$6:$A$165,A101)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T101" s="23" t="str">
+        <x:f>IF(COUNTA($A101)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C101),C101,""),IF('Status'!$B$14=2,IF(ISNUMBER(D101),D101,""),IF('Status'!$B$14=3,IF(ISNUMBER(E101),E101,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J101),J101,""),IF('Status'!$B$14=2,IF(ISNUMBER(K101),K101,""),IF('Status'!$B$14=3,IF(ISNUMBER(L101),L101,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="6"/>
@@ -6337,6 +6685,9 @@
       <x:c r="S102" s="2" t="str">
         <x:f>IF(COUNTA(A102)=0,"",IF(COUNTIFS($A$6:$A$165,A102)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T102" s="23" t="str">
+        <x:f>IF(COUNTA($A102)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C102),C102,""),IF('Status'!$B$14=2,IF(ISNUMBER(D102),D102,""),IF('Status'!$B$14=3,IF(ISNUMBER(E102),E102,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J102),J102,""),IF('Status'!$B$14=2,IF(ISNUMBER(K102),K102,""),IF('Status'!$B$14=3,IF(ISNUMBER(L102),L102,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="6"/>
@@ -6392,6 +6743,9 @@
       <x:c r="S103" s="2" t="str">
         <x:f>IF(COUNTA(A103)=0,"",IF(COUNTIFS($A$6:$A$165,A103)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T103" s="23" t="str">
+        <x:f>IF(COUNTA($A103)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C103),C103,""),IF('Status'!$B$14=2,IF(ISNUMBER(D103),D103,""),IF('Status'!$B$14=3,IF(ISNUMBER(E103),E103,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J103),J103,""),IF('Status'!$B$14=2,IF(ISNUMBER(K103),K103,""),IF('Status'!$B$14=3,IF(ISNUMBER(L103),L103,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="6"/>
@@ -6447,6 +6801,9 @@
       <x:c r="S104" s="2" t="str">
         <x:f>IF(COUNTA(A104)=0,"",IF(COUNTIFS($A$6:$A$165,A104)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T104" s="23" t="str">
+        <x:f>IF(COUNTA($A104)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C104),C104,""),IF('Status'!$B$14=2,IF(ISNUMBER(D104),D104,""),IF('Status'!$B$14=3,IF(ISNUMBER(E104),E104,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J104),J104,""),IF('Status'!$B$14=2,IF(ISNUMBER(K104),K104,""),IF('Status'!$B$14=3,IF(ISNUMBER(L104),L104,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="6"/>
@@ -6502,6 +6859,9 @@
       <x:c r="S105" s="2" t="str">
         <x:f>IF(COUNTA(A105)=0,"",IF(COUNTIFS($A$6:$A$165,A105)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T105" s="23" t="str">
+        <x:f>IF(COUNTA($A105)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C105),C105,""),IF('Status'!$B$14=2,IF(ISNUMBER(D105),D105,""),IF('Status'!$B$14=3,IF(ISNUMBER(E105),E105,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J105),J105,""),IF('Status'!$B$14=2,IF(ISNUMBER(K105),K105,""),IF('Status'!$B$14=3,IF(ISNUMBER(L105),L105,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="6"/>
@@ -6557,6 +6917,9 @@
       <x:c r="S106" s="2" t="str">
         <x:f>IF(COUNTA(A106)=0,"",IF(COUNTIFS($A$6:$A$165,A106)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T106" s="23" t="str">
+        <x:f>IF(COUNTA($A106)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C106),C106,""),IF('Status'!$B$14=2,IF(ISNUMBER(D106),D106,""),IF('Status'!$B$14=3,IF(ISNUMBER(E106),E106,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J106),J106,""),IF('Status'!$B$14=2,IF(ISNUMBER(K106),K106,""),IF('Status'!$B$14=3,IF(ISNUMBER(L106),L106,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="6"/>
@@ -6612,6 +6975,9 @@
       <x:c r="S107" s="2" t="str">
         <x:f>IF(COUNTA(A107)=0,"",IF(COUNTIFS($A$6:$A$165,A107)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T107" s="23" t="str">
+        <x:f>IF(COUNTA($A107)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C107),C107,""),IF('Status'!$B$14=2,IF(ISNUMBER(D107),D107,""),IF('Status'!$B$14=3,IF(ISNUMBER(E107),E107,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J107),J107,""),IF('Status'!$B$14=2,IF(ISNUMBER(K107),K107,""),IF('Status'!$B$14=3,IF(ISNUMBER(L107),L107,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="6"/>
@@ -6667,6 +7033,9 @@
       <x:c r="S108" s="2" t="str">
         <x:f>IF(COUNTA(A108)=0,"",IF(COUNTIFS($A$6:$A$165,A108)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T108" s="23" t="str">
+        <x:f>IF(COUNTA($A108)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C108),C108,""),IF('Status'!$B$14=2,IF(ISNUMBER(D108),D108,""),IF('Status'!$B$14=3,IF(ISNUMBER(E108),E108,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J108),J108,""),IF('Status'!$B$14=2,IF(ISNUMBER(K108),K108,""),IF('Status'!$B$14=3,IF(ISNUMBER(L108),L108,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="6"/>
@@ -6722,6 +7091,9 @@
       <x:c r="S109" s="2" t="str">
         <x:f>IF(COUNTA(A109)=0,"",IF(COUNTIFS($A$6:$A$165,A109)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T109" s="23" t="str">
+        <x:f>IF(COUNTA($A109)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C109),C109,""),IF('Status'!$B$14=2,IF(ISNUMBER(D109),D109,""),IF('Status'!$B$14=3,IF(ISNUMBER(E109),E109,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J109),J109,""),IF('Status'!$B$14=2,IF(ISNUMBER(K109),K109,""),IF('Status'!$B$14=3,IF(ISNUMBER(L109),L109,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="6"/>
@@ -6777,6 +7149,9 @@
       <x:c r="S110" s="2" t="str">
         <x:f>IF(COUNTA(A110)=0,"",IF(COUNTIFS($A$6:$A$165,A110)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T110" s="23" t="str">
+        <x:f>IF(COUNTA($A110)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C110),C110,""),IF('Status'!$B$14=2,IF(ISNUMBER(D110),D110,""),IF('Status'!$B$14=3,IF(ISNUMBER(E110),E110,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J110),J110,""),IF('Status'!$B$14=2,IF(ISNUMBER(K110),K110,""),IF('Status'!$B$14=3,IF(ISNUMBER(L110),L110,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="6"/>
@@ -6832,6 +7207,9 @@
       <x:c r="S111" s="2" t="str">
         <x:f>IF(COUNTA(A111)=0,"",IF(COUNTIFS($A$6:$A$165,A111)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T111" s="23" t="str">
+        <x:f>IF(COUNTA($A111)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C111),C111,""),IF('Status'!$B$14=2,IF(ISNUMBER(D111),D111,""),IF('Status'!$B$14=3,IF(ISNUMBER(E111),E111,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J111),J111,""),IF('Status'!$B$14=2,IF(ISNUMBER(K111),K111,""),IF('Status'!$B$14=3,IF(ISNUMBER(L111),L111,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="6"/>
@@ -6887,6 +7265,9 @@
       <x:c r="S112" s="2" t="str">
         <x:f>IF(COUNTA(A112)=0,"",IF(COUNTIFS($A$6:$A$165,A112)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T112" s="23" t="str">
+        <x:f>IF(COUNTA($A112)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C112),C112,""),IF('Status'!$B$14=2,IF(ISNUMBER(D112),D112,""),IF('Status'!$B$14=3,IF(ISNUMBER(E112),E112,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J112),J112,""),IF('Status'!$B$14=2,IF(ISNUMBER(K112),K112,""),IF('Status'!$B$14=3,IF(ISNUMBER(L112),L112,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="6"/>
@@ -6942,6 +7323,9 @@
       <x:c r="S113" s="2" t="str">
         <x:f>IF(COUNTA(A113)=0,"",IF(COUNTIFS($A$6:$A$165,A113)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T113" s="23" t="str">
+        <x:f>IF(COUNTA($A113)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C113),C113,""),IF('Status'!$B$14=2,IF(ISNUMBER(D113),D113,""),IF('Status'!$B$14=3,IF(ISNUMBER(E113),E113,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J113),J113,""),IF('Status'!$B$14=2,IF(ISNUMBER(K113),K113,""),IF('Status'!$B$14=3,IF(ISNUMBER(L113),L113,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="6"/>
@@ -6997,6 +7381,9 @@
       <x:c r="S114" s="2" t="str">
         <x:f>IF(COUNTA(A114)=0,"",IF(COUNTIFS($A$6:$A$165,A114)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T114" s="23" t="str">
+        <x:f>IF(COUNTA($A114)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C114),C114,""),IF('Status'!$B$14=2,IF(ISNUMBER(D114),D114,""),IF('Status'!$B$14=3,IF(ISNUMBER(E114),E114,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J114),J114,""),IF('Status'!$B$14=2,IF(ISNUMBER(K114),K114,""),IF('Status'!$B$14=3,IF(ISNUMBER(L114),L114,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="6"/>
@@ -7052,6 +7439,9 @@
       <x:c r="S115" s="2" t="str">
         <x:f>IF(COUNTA(A115)=0,"",IF(COUNTIFS($A$6:$A$165,A115)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T115" s="23" t="str">
+        <x:f>IF(COUNTA($A115)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C115),C115,""),IF('Status'!$B$14=2,IF(ISNUMBER(D115),D115,""),IF('Status'!$B$14=3,IF(ISNUMBER(E115),E115,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J115),J115,""),IF('Status'!$B$14=2,IF(ISNUMBER(K115),K115,""),IF('Status'!$B$14=3,IF(ISNUMBER(L115),L115,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="6"/>
@@ -7107,6 +7497,9 @@
       <x:c r="S116" s="2" t="str">
         <x:f>IF(COUNTA(A116)=0,"",IF(COUNTIFS($A$6:$A$165,A116)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T116" s="23" t="str">
+        <x:f>IF(COUNTA($A116)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C116),C116,""),IF('Status'!$B$14=2,IF(ISNUMBER(D116),D116,""),IF('Status'!$B$14=3,IF(ISNUMBER(E116),E116,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J116),J116,""),IF('Status'!$B$14=2,IF(ISNUMBER(K116),K116,""),IF('Status'!$B$14=3,IF(ISNUMBER(L116),L116,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="6"/>
@@ -7162,6 +7555,9 @@
       <x:c r="S117" s="2" t="str">
         <x:f>IF(COUNTA(A117)=0,"",IF(COUNTIFS($A$6:$A$165,A117)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T117" s="23" t="str">
+        <x:f>IF(COUNTA($A117)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C117),C117,""),IF('Status'!$B$14=2,IF(ISNUMBER(D117),D117,""),IF('Status'!$B$14=3,IF(ISNUMBER(E117),E117,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J117),J117,""),IF('Status'!$B$14=2,IF(ISNUMBER(K117),K117,""),IF('Status'!$B$14=3,IF(ISNUMBER(L117),L117,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="6"/>
@@ -7217,6 +7613,9 @@
       <x:c r="S118" s="2" t="str">
         <x:f>IF(COUNTA(A118)=0,"",IF(COUNTIFS($A$6:$A$165,A118)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T118" s="23" t="str">
+        <x:f>IF(COUNTA($A118)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C118),C118,""),IF('Status'!$B$14=2,IF(ISNUMBER(D118),D118,""),IF('Status'!$B$14=3,IF(ISNUMBER(E118),E118,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J118),J118,""),IF('Status'!$B$14=2,IF(ISNUMBER(K118),K118,""),IF('Status'!$B$14=3,IF(ISNUMBER(L118),L118,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="6"/>
@@ -7272,6 +7671,9 @@
       <x:c r="S119" s="2" t="str">
         <x:f>IF(COUNTA(A119)=0,"",IF(COUNTIFS($A$6:$A$165,A119)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T119" s="23" t="str">
+        <x:f>IF(COUNTA($A119)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C119),C119,""),IF('Status'!$B$14=2,IF(ISNUMBER(D119),D119,""),IF('Status'!$B$14=3,IF(ISNUMBER(E119),E119,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J119),J119,""),IF('Status'!$B$14=2,IF(ISNUMBER(K119),K119,""),IF('Status'!$B$14=3,IF(ISNUMBER(L119),L119,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="6"/>
@@ -7327,6 +7729,9 @@
       <x:c r="S120" s="2" t="str">
         <x:f>IF(COUNTA(A120)=0,"",IF(COUNTIFS($A$6:$A$165,A120)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T120" s="23" t="str">
+        <x:f>IF(COUNTA($A120)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C120),C120,""),IF('Status'!$B$14=2,IF(ISNUMBER(D120),D120,""),IF('Status'!$B$14=3,IF(ISNUMBER(E120),E120,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J120),J120,""),IF('Status'!$B$14=2,IF(ISNUMBER(K120),K120,""),IF('Status'!$B$14=3,IF(ISNUMBER(L120),L120,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="6"/>
@@ -7382,6 +7787,9 @@
       <x:c r="S121" s="2" t="str">
         <x:f>IF(COUNTA(A121)=0,"",IF(COUNTIFS($A$6:$A$165,A121)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T121" s="23" t="str">
+        <x:f>IF(COUNTA($A121)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C121),C121,""),IF('Status'!$B$14=2,IF(ISNUMBER(D121),D121,""),IF('Status'!$B$14=3,IF(ISNUMBER(E121),E121,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J121),J121,""),IF('Status'!$B$14=2,IF(ISNUMBER(K121),K121,""),IF('Status'!$B$14=3,IF(ISNUMBER(L121),L121,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="6"/>
@@ -7437,6 +7845,9 @@
       <x:c r="S122" s="2" t="str">
         <x:f>IF(COUNTA(A122)=0,"",IF(COUNTIFS($A$6:$A$165,A122)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T122" s="23" t="str">
+        <x:f>IF(COUNTA($A122)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C122),C122,""),IF('Status'!$B$14=2,IF(ISNUMBER(D122),D122,""),IF('Status'!$B$14=3,IF(ISNUMBER(E122),E122,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J122),J122,""),IF('Status'!$B$14=2,IF(ISNUMBER(K122),K122,""),IF('Status'!$B$14=3,IF(ISNUMBER(L122),L122,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="6"/>
@@ -7492,6 +7903,9 @@
       <x:c r="S123" s="2" t="str">
         <x:f>IF(COUNTA(A123)=0,"",IF(COUNTIFS($A$6:$A$165,A123)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T123" s="23" t="str">
+        <x:f>IF(COUNTA($A123)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C123),C123,""),IF('Status'!$B$14=2,IF(ISNUMBER(D123),D123,""),IF('Status'!$B$14=3,IF(ISNUMBER(E123),E123,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J123),J123,""),IF('Status'!$B$14=2,IF(ISNUMBER(K123),K123,""),IF('Status'!$B$14=3,IF(ISNUMBER(L123),L123,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="6"/>
@@ -7547,6 +7961,9 @@
       <x:c r="S124" s="2" t="str">
         <x:f>IF(COUNTA(A124)=0,"",IF(COUNTIFS($A$6:$A$165,A124)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T124" s="23" t="str">
+        <x:f>IF(COUNTA($A124)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C124),C124,""),IF('Status'!$B$14=2,IF(ISNUMBER(D124),D124,""),IF('Status'!$B$14=3,IF(ISNUMBER(E124),E124,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J124),J124,""),IF('Status'!$B$14=2,IF(ISNUMBER(K124),K124,""),IF('Status'!$B$14=3,IF(ISNUMBER(L124),L124,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="6"/>
@@ -7602,6 +8019,9 @@
       <x:c r="S125" s="2" t="str">
         <x:f>IF(COUNTA(A125)=0,"",IF(COUNTIFS($A$6:$A$165,A125)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T125" s="23" t="str">
+        <x:f>IF(COUNTA($A125)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C125),C125,""),IF('Status'!$B$14=2,IF(ISNUMBER(D125),D125,""),IF('Status'!$B$14=3,IF(ISNUMBER(E125),E125,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J125),J125,""),IF('Status'!$B$14=2,IF(ISNUMBER(K125),K125,""),IF('Status'!$B$14=3,IF(ISNUMBER(L125),L125,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="6"/>
@@ -7657,6 +8077,9 @@
       <x:c r="S126" s="2" t="str">
         <x:f>IF(COUNTA(A126)=0,"",IF(COUNTIFS($A$6:$A$165,A126)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T126" s="23" t="str">
+        <x:f>IF(COUNTA($A126)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C126),C126,""),IF('Status'!$B$14=2,IF(ISNUMBER(D126),D126,""),IF('Status'!$B$14=3,IF(ISNUMBER(E126),E126,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J126),J126,""),IF('Status'!$B$14=2,IF(ISNUMBER(K126),K126,""),IF('Status'!$B$14=3,IF(ISNUMBER(L126),L126,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="6"/>
@@ -7712,6 +8135,9 @@
       <x:c r="S127" s="2" t="str">
         <x:f>IF(COUNTA(A127)=0,"",IF(COUNTIFS($A$6:$A$165,A127)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T127" s="23" t="str">
+        <x:f>IF(COUNTA($A127)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C127),C127,""),IF('Status'!$B$14=2,IF(ISNUMBER(D127),D127,""),IF('Status'!$B$14=3,IF(ISNUMBER(E127),E127,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J127),J127,""),IF('Status'!$B$14=2,IF(ISNUMBER(K127),K127,""),IF('Status'!$B$14=3,IF(ISNUMBER(L127),L127,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="6"/>
@@ -7767,6 +8193,9 @@
       <x:c r="S128" s="2" t="str">
         <x:f>IF(COUNTA(A128)=0,"",IF(COUNTIFS($A$6:$A$165,A128)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T128" s="23" t="str">
+        <x:f>IF(COUNTA($A128)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C128),C128,""),IF('Status'!$B$14=2,IF(ISNUMBER(D128),D128,""),IF('Status'!$B$14=3,IF(ISNUMBER(E128),E128,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J128),J128,""),IF('Status'!$B$14=2,IF(ISNUMBER(K128),K128,""),IF('Status'!$B$14=3,IF(ISNUMBER(L128),L128,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="6"/>
@@ -7822,6 +8251,9 @@
       <x:c r="S129" s="2" t="str">
         <x:f>IF(COUNTA(A129)=0,"",IF(COUNTIFS($A$6:$A$165,A129)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T129" s="23" t="str">
+        <x:f>IF(COUNTA($A129)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C129),C129,""),IF('Status'!$B$14=2,IF(ISNUMBER(D129),D129,""),IF('Status'!$B$14=3,IF(ISNUMBER(E129),E129,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J129),J129,""),IF('Status'!$B$14=2,IF(ISNUMBER(K129),K129,""),IF('Status'!$B$14=3,IF(ISNUMBER(L129),L129,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="6"/>
@@ -7877,6 +8309,9 @@
       <x:c r="S130" s="2" t="str">
         <x:f>IF(COUNTA(A130)=0,"",IF(COUNTIFS($A$6:$A$165,A130)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T130" s="23" t="str">
+        <x:f>IF(COUNTA($A130)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C130),C130,""),IF('Status'!$B$14=2,IF(ISNUMBER(D130),D130,""),IF('Status'!$B$14=3,IF(ISNUMBER(E130),E130,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J130),J130,""),IF('Status'!$B$14=2,IF(ISNUMBER(K130),K130,""),IF('Status'!$B$14=3,IF(ISNUMBER(L130),L130,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="6"/>
@@ -7932,6 +8367,9 @@
       <x:c r="S131" s="2" t="str">
         <x:f>IF(COUNTA(A131)=0,"",IF(COUNTIFS($A$6:$A$165,A131)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T131" s="23" t="str">
+        <x:f>IF(COUNTA($A131)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C131),C131,""),IF('Status'!$B$14=2,IF(ISNUMBER(D131),D131,""),IF('Status'!$B$14=3,IF(ISNUMBER(E131),E131,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J131),J131,""),IF('Status'!$B$14=2,IF(ISNUMBER(K131),K131,""),IF('Status'!$B$14=3,IF(ISNUMBER(L131),L131,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="6"/>
@@ -7987,6 +8425,9 @@
       <x:c r="S132" s="2" t="str">
         <x:f>IF(COUNTA(A132)=0,"",IF(COUNTIFS($A$6:$A$165,A132)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T132" s="23" t="str">
+        <x:f>IF(COUNTA($A132)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C132),C132,""),IF('Status'!$B$14=2,IF(ISNUMBER(D132),D132,""),IF('Status'!$B$14=3,IF(ISNUMBER(E132),E132,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J132),J132,""),IF('Status'!$B$14=2,IF(ISNUMBER(K132),K132,""),IF('Status'!$B$14=3,IF(ISNUMBER(L132),L132,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="6"/>
@@ -8042,6 +8483,9 @@
       <x:c r="S133" s="2" t="str">
         <x:f>IF(COUNTA(A133)=0,"",IF(COUNTIFS($A$6:$A$165,A133)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T133" s="23" t="str">
+        <x:f>IF(COUNTA($A133)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C133),C133,""),IF('Status'!$B$14=2,IF(ISNUMBER(D133),D133,""),IF('Status'!$B$14=3,IF(ISNUMBER(E133),E133,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J133),J133,""),IF('Status'!$B$14=2,IF(ISNUMBER(K133),K133,""),IF('Status'!$B$14=3,IF(ISNUMBER(L133),L133,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="6"/>
@@ -8097,6 +8541,9 @@
       <x:c r="S134" s="2" t="str">
         <x:f>IF(COUNTA(A134)=0,"",IF(COUNTIFS($A$6:$A$165,A134)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T134" s="23" t="str">
+        <x:f>IF(COUNTA($A134)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C134),C134,""),IF('Status'!$B$14=2,IF(ISNUMBER(D134),D134,""),IF('Status'!$B$14=3,IF(ISNUMBER(E134),E134,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J134),J134,""),IF('Status'!$B$14=2,IF(ISNUMBER(K134),K134,""),IF('Status'!$B$14=3,IF(ISNUMBER(L134),L134,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="6"/>
@@ -8152,6 +8599,9 @@
       <x:c r="S135" s="2" t="str">
         <x:f>IF(COUNTA(A135)=0,"",IF(COUNTIFS($A$6:$A$165,A135)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T135" s="23" t="str">
+        <x:f>IF(COUNTA($A135)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C135),C135,""),IF('Status'!$B$14=2,IF(ISNUMBER(D135),D135,""),IF('Status'!$B$14=3,IF(ISNUMBER(E135),E135,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J135),J135,""),IF('Status'!$B$14=2,IF(ISNUMBER(K135),K135,""),IF('Status'!$B$14=3,IF(ISNUMBER(L135),L135,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="6"/>
@@ -8207,6 +8657,9 @@
       <x:c r="S136" s="2" t="str">
         <x:f>IF(COUNTA(A136)=0,"",IF(COUNTIFS($A$6:$A$165,A136)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T136" s="23" t="str">
+        <x:f>IF(COUNTA($A136)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C136),C136,""),IF('Status'!$B$14=2,IF(ISNUMBER(D136),D136,""),IF('Status'!$B$14=3,IF(ISNUMBER(E136),E136,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J136),J136,""),IF('Status'!$B$14=2,IF(ISNUMBER(K136),K136,""),IF('Status'!$B$14=3,IF(ISNUMBER(L136),L136,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="6"/>
@@ -8262,6 +8715,9 @@
       <x:c r="S137" s="2" t="str">
         <x:f>IF(COUNTA(A137)=0,"",IF(COUNTIFS($A$6:$A$165,A137)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T137" s="23" t="str">
+        <x:f>IF(COUNTA($A137)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C137),C137,""),IF('Status'!$B$14=2,IF(ISNUMBER(D137),D137,""),IF('Status'!$B$14=3,IF(ISNUMBER(E137),E137,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J137),J137,""),IF('Status'!$B$14=2,IF(ISNUMBER(K137),K137,""),IF('Status'!$B$14=3,IF(ISNUMBER(L137),L137,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="6"/>
@@ -8317,6 +8773,9 @@
       <x:c r="S138" s="2" t="str">
         <x:f>IF(COUNTA(A138)=0,"",IF(COUNTIFS($A$6:$A$165,A138)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T138" s="23" t="str">
+        <x:f>IF(COUNTA($A138)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C138),C138,""),IF('Status'!$B$14=2,IF(ISNUMBER(D138),D138,""),IF('Status'!$B$14=3,IF(ISNUMBER(E138),E138,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J138),J138,""),IF('Status'!$B$14=2,IF(ISNUMBER(K138),K138,""),IF('Status'!$B$14=3,IF(ISNUMBER(L138),L138,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="6"/>
@@ -8372,6 +8831,9 @@
       <x:c r="S139" s="2" t="str">
         <x:f>IF(COUNTA(A139)=0,"",IF(COUNTIFS($A$6:$A$165,A139)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T139" s="23" t="str">
+        <x:f>IF(COUNTA($A139)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C139),C139,""),IF('Status'!$B$14=2,IF(ISNUMBER(D139),D139,""),IF('Status'!$B$14=3,IF(ISNUMBER(E139),E139,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J139),J139,""),IF('Status'!$B$14=2,IF(ISNUMBER(K139),K139,""),IF('Status'!$B$14=3,IF(ISNUMBER(L139),L139,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="6"/>
@@ -8427,6 +8889,9 @@
       <x:c r="S140" s="2" t="str">
         <x:f>IF(COUNTA(A140)=0,"",IF(COUNTIFS($A$6:$A$165,A140)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T140" s="23" t="str">
+        <x:f>IF(COUNTA($A140)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C140),C140,""),IF('Status'!$B$14=2,IF(ISNUMBER(D140),D140,""),IF('Status'!$B$14=3,IF(ISNUMBER(E140),E140,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J140),J140,""),IF('Status'!$B$14=2,IF(ISNUMBER(K140),K140,""),IF('Status'!$B$14=3,IF(ISNUMBER(L140),L140,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="6"/>
@@ -8482,6 +8947,9 @@
       <x:c r="S141" s="2" t="str">
         <x:f>IF(COUNTA(A141)=0,"",IF(COUNTIFS($A$6:$A$165,A141)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T141" s="23" t="str">
+        <x:f>IF(COUNTA($A141)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C141),C141,""),IF('Status'!$B$14=2,IF(ISNUMBER(D141),D141,""),IF('Status'!$B$14=3,IF(ISNUMBER(E141),E141,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J141),J141,""),IF('Status'!$B$14=2,IF(ISNUMBER(K141),K141,""),IF('Status'!$B$14=3,IF(ISNUMBER(L141),L141,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="6"/>
@@ -8537,6 +9005,9 @@
       <x:c r="S142" s="2" t="str">
         <x:f>IF(COUNTA(A142)=0,"",IF(COUNTIFS($A$6:$A$165,A142)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T142" s="23" t="str">
+        <x:f>IF(COUNTA($A142)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C142),C142,""),IF('Status'!$B$14=2,IF(ISNUMBER(D142),D142,""),IF('Status'!$B$14=3,IF(ISNUMBER(E142),E142,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J142),J142,""),IF('Status'!$B$14=2,IF(ISNUMBER(K142),K142,""),IF('Status'!$B$14=3,IF(ISNUMBER(L142),L142,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="6"/>
@@ -8592,6 +9063,9 @@
       <x:c r="S143" s="2" t="str">
         <x:f>IF(COUNTA(A143)=0,"",IF(COUNTIFS($A$6:$A$165,A143)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T143" s="23" t="str">
+        <x:f>IF(COUNTA($A143)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C143),C143,""),IF('Status'!$B$14=2,IF(ISNUMBER(D143),D143,""),IF('Status'!$B$14=3,IF(ISNUMBER(E143),E143,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J143),J143,""),IF('Status'!$B$14=2,IF(ISNUMBER(K143),K143,""),IF('Status'!$B$14=3,IF(ISNUMBER(L143),L143,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="6"/>
@@ -8647,6 +9121,9 @@
       <x:c r="S144" s="2" t="str">
         <x:f>IF(COUNTA(A144)=0,"",IF(COUNTIFS($A$6:$A$165,A144)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T144" s="23" t="str">
+        <x:f>IF(COUNTA($A144)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C144),C144,""),IF('Status'!$B$14=2,IF(ISNUMBER(D144),D144,""),IF('Status'!$B$14=3,IF(ISNUMBER(E144),E144,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J144),J144,""),IF('Status'!$B$14=2,IF(ISNUMBER(K144),K144,""),IF('Status'!$B$14=3,IF(ISNUMBER(L144),L144,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="6"/>
@@ -8702,6 +9179,9 @@
       <x:c r="S145" s="2" t="str">
         <x:f>IF(COUNTA(A145)=0,"",IF(COUNTIFS($A$6:$A$165,A145)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T145" s="23" t="str">
+        <x:f>IF(COUNTA($A145)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C145),C145,""),IF('Status'!$B$14=2,IF(ISNUMBER(D145),D145,""),IF('Status'!$B$14=3,IF(ISNUMBER(E145),E145,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J145),J145,""),IF('Status'!$B$14=2,IF(ISNUMBER(K145),K145,""),IF('Status'!$B$14=3,IF(ISNUMBER(L145),L145,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="6"/>
@@ -8757,6 +9237,9 @@
       <x:c r="S146" s="2" t="str">
         <x:f>IF(COUNTA(A146)=0,"",IF(COUNTIFS($A$6:$A$165,A146)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T146" s="23" t="str">
+        <x:f>IF(COUNTA($A146)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C146),C146,""),IF('Status'!$B$14=2,IF(ISNUMBER(D146),D146,""),IF('Status'!$B$14=3,IF(ISNUMBER(E146),E146,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J146),J146,""),IF('Status'!$B$14=2,IF(ISNUMBER(K146),K146,""),IF('Status'!$B$14=3,IF(ISNUMBER(L146),L146,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="6"/>
@@ -8812,6 +9295,9 @@
       <x:c r="S147" s="2" t="str">
         <x:f>IF(COUNTA(A147)=0,"",IF(COUNTIFS($A$6:$A$165,A147)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T147" s="23" t="str">
+        <x:f>IF(COUNTA($A147)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C147),C147,""),IF('Status'!$B$14=2,IF(ISNUMBER(D147),D147,""),IF('Status'!$B$14=3,IF(ISNUMBER(E147),E147,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J147),J147,""),IF('Status'!$B$14=2,IF(ISNUMBER(K147),K147,""),IF('Status'!$B$14=3,IF(ISNUMBER(L147),L147,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="6"/>
@@ -8867,6 +9353,9 @@
       <x:c r="S148" s="2" t="str">
         <x:f>IF(COUNTA(A148)=0,"",IF(COUNTIFS($A$6:$A$165,A148)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T148" s="23" t="str">
+        <x:f>IF(COUNTA($A148)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C148),C148,""),IF('Status'!$B$14=2,IF(ISNUMBER(D148),D148,""),IF('Status'!$B$14=3,IF(ISNUMBER(E148),E148,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J148),J148,""),IF('Status'!$B$14=2,IF(ISNUMBER(K148),K148,""),IF('Status'!$B$14=3,IF(ISNUMBER(L148),L148,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="6"/>
@@ -8922,6 +9411,9 @@
       <x:c r="S149" s="2" t="str">
         <x:f>IF(COUNTA(A149)=0,"",IF(COUNTIFS($A$6:$A$165,A149)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T149" s="23" t="str">
+        <x:f>IF(COUNTA($A149)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C149),C149,""),IF('Status'!$B$14=2,IF(ISNUMBER(D149),D149,""),IF('Status'!$B$14=3,IF(ISNUMBER(E149),E149,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J149),J149,""),IF('Status'!$B$14=2,IF(ISNUMBER(K149),K149,""),IF('Status'!$B$14=3,IF(ISNUMBER(L149),L149,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="6"/>
@@ -8977,6 +9469,9 @@
       <x:c r="S150" s="2" t="str">
         <x:f>IF(COUNTA(A150)=0,"",IF(COUNTIFS($A$6:$A$165,A150)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T150" s="23" t="str">
+        <x:f>IF(COUNTA($A150)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C150),C150,""),IF('Status'!$B$14=2,IF(ISNUMBER(D150),D150,""),IF('Status'!$B$14=3,IF(ISNUMBER(E150),E150,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J150),J150,""),IF('Status'!$B$14=2,IF(ISNUMBER(K150),K150,""),IF('Status'!$B$14=3,IF(ISNUMBER(L150),L150,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="6"/>
@@ -9032,6 +9527,9 @@
       <x:c r="S151" s="2" t="str">
         <x:f>IF(COUNTA(A151)=0,"",IF(COUNTIFS($A$6:$A$165,A151)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T151" s="23" t="str">
+        <x:f>IF(COUNTA($A151)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C151),C151,""),IF('Status'!$B$14=2,IF(ISNUMBER(D151),D151,""),IF('Status'!$B$14=3,IF(ISNUMBER(E151),E151,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J151),J151,""),IF('Status'!$B$14=2,IF(ISNUMBER(K151),K151,""),IF('Status'!$B$14=3,IF(ISNUMBER(L151),L151,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="6"/>
@@ -9087,6 +9585,9 @@
       <x:c r="S152" s="2" t="str">
         <x:f>IF(COUNTA(A152)=0,"",IF(COUNTIFS($A$6:$A$165,A152)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T152" s="23" t="str">
+        <x:f>IF(COUNTA($A152)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C152),C152,""),IF('Status'!$B$14=2,IF(ISNUMBER(D152),D152,""),IF('Status'!$B$14=3,IF(ISNUMBER(E152),E152,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J152),J152,""),IF('Status'!$B$14=2,IF(ISNUMBER(K152),K152,""),IF('Status'!$B$14=3,IF(ISNUMBER(L152),L152,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="6"/>
@@ -9142,6 +9643,9 @@
       <x:c r="S153" s="2" t="str">
         <x:f>IF(COUNTA(A153)=0,"",IF(COUNTIFS($A$6:$A$165,A153)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T153" s="23" t="str">
+        <x:f>IF(COUNTA($A153)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C153),C153,""),IF('Status'!$B$14=2,IF(ISNUMBER(D153),D153,""),IF('Status'!$B$14=3,IF(ISNUMBER(E153),E153,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J153),J153,""),IF('Status'!$B$14=2,IF(ISNUMBER(K153),K153,""),IF('Status'!$B$14=3,IF(ISNUMBER(L153),L153,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="6"/>
@@ -9197,6 +9701,9 @@
       <x:c r="S154" s="2" t="str">
         <x:f>IF(COUNTA(A154)=0,"",IF(COUNTIFS($A$6:$A$165,A154)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T154" s="23" t="str">
+        <x:f>IF(COUNTA($A154)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C154),C154,""),IF('Status'!$B$14=2,IF(ISNUMBER(D154),D154,""),IF('Status'!$B$14=3,IF(ISNUMBER(E154),E154,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J154),J154,""),IF('Status'!$B$14=2,IF(ISNUMBER(K154),K154,""),IF('Status'!$B$14=3,IF(ISNUMBER(L154),L154,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="6"/>
@@ -9252,6 +9759,9 @@
       <x:c r="S155" s="2" t="str">
         <x:f>IF(COUNTA(A155)=0,"",IF(COUNTIFS($A$6:$A$165,A155)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T155" s="23" t="str">
+        <x:f>IF(COUNTA($A155)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C155),C155,""),IF('Status'!$B$14=2,IF(ISNUMBER(D155),D155,""),IF('Status'!$B$14=3,IF(ISNUMBER(E155),E155,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J155),J155,""),IF('Status'!$B$14=2,IF(ISNUMBER(K155),K155,""),IF('Status'!$B$14=3,IF(ISNUMBER(L155),L155,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="6"/>
@@ -9307,6 +9817,9 @@
       <x:c r="S156" s="2" t="str">
         <x:f>IF(COUNTA(A156)=0,"",IF(COUNTIFS($A$6:$A$165,A156)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T156" s="23" t="str">
+        <x:f>IF(COUNTA($A156)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C156),C156,""),IF('Status'!$B$14=2,IF(ISNUMBER(D156),D156,""),IF('Status'!$B$14=3,IF(ISNUMBER(E156),E156,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J156),J156,""),IF('Status'!$B$14=2,IF(ISNUMBER(K156),K156,""),IF('Status'!$B$14=3,IF(ISNUMBER(L156),L156,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="6"/>
@@ -9362,6 +9875,9 @@
       <x:c r="S157" s="2" t="str">
         <x:f>IF(COUNTA(A157)=0,"",IF(COUNTIFS($A$6:$A$165,A157)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T157" s="23" t="str">
+        <x:f>IF(COUNTA($A157)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C157),C157,""),IF('Status'!$B$14=2,IF(ISNUMBER(D157),D157,""),IF('Status'!$B$14=3,IF(ISNUMBER(E157),E157,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J157),J157,""),IF('Status'!$B$14=2,IF(ISNUMBER(K157),K157,""),IF('Status'!$B$14=3,IF(ISNUMBER(L157),L157,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="6"/>
@@ -9417,6 +9933,9 @@
       <x:c r="S158" s="2" t="str">
         <x:f>IF(COUNTA(A158)=0,"",IF(COUNTIFS($A$6:$A$165,A158)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T158" s="23" t="str">
+        <x:f>IF(COUNTA($A158)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C158),C158,""),IF('Status'!$B$14=2,IF(ISNUMBER(D158),D158,""),IF('Status'!$B$14=3,IF(ISNUMBER(E158),E158,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J158),J158,""),IF('Status'!$B$14=2,IF(ISNUMBER(K158),K158,""),IF('Status'!$B$14=3,IF(ISNUMBER(L158),L158,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="6"/>
@@ -9472,6 +9991,9 @@
       <x:c r="S159" s="2" t="str">
         <x:f>IF(COUNTA(A159)=0,"",IF(COUNTIFS($A$6:$A$165,A159)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T159" s="23" t="str">
+        <x:f>IF(COUNTA($A159)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C159),C159,""),IF('Status'!$B$14=2,IF(ISNUMBER(D159),D159,""),IF('Status'!$B$14=3,IF(ISNUMBER(E159),E159,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J159),J159,""),IF('Status'!$B$14=2,IF(ISNUMBER(K159),K159,""),IF('Status'!$B$14=3,IF(ISNUMBER(L159),L159,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="6"/>
@@ -9527,6 +10049,9 @@
       <x:c r="S160" s="2" t="str">
         <x:f>IF(COUNTA(A160)=0,"",IF(COUNTIFS($A$6:$A$165,A160)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T160" s="23" t="str">
+        <x:f>IF(COUNTA($A160)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C160),C160,""),IF('Status'!$B$14=2,IF(ISNUMBER(D160),D160,""),IF('Status'!$B$14=3,IF(ISNUMBER(E160),E160,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J160),J160,""),IF('Status'!$B$14=2,IF(ISNUMBER(K160),K160,""),IF('Status'!$B$14=3,IF(ISNUMBER(L160),L160,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="6"/>
@@ -9582,6 +10107,9 @@
       <x:c r="S161" s="2" t="str">
         <x:f>IF(COUNTA(A161)=0,"",IF(COUNTIFS($A$6:$A$165,A161)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T161" s="23" t="str">
+        <x:f>IF(COUNTA($A161)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C161),C161,""),IF('Status'!$B$14=2,IF(ISNUMBER(D161),D161,""),IF('Status'!$B$14=3,IF(ISNUMBER(E161),E161,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J161),J161,""),IF('Status'!$B$14=2,IF(ISNUMBER(K161),K161,""),IF('Status'!$B$14=3,IF(ISNUMBER(L161),L161,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="6"/>
@@ -9637,6 +10165,9 @@
       <x:c r="S162" s="2" t="str">
         <x:f>IF(COUNTA(A162)=0,"",IF(COUNTIFS($A$6:$A$165,A162)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T162" s="23" t="str">
+        <x:f>IF(COUNTA($A162)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C162),C162,""),IF('Status'!$B$14=2,IF(ISNUMBER(D162),D162,""),IF('Status'!$B$14=3,IF(ISNUMBER(E162),E162,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J162),J162,""),IF('Status'!$B$14=2,IF(ISNUMBER(K162),K162,""),IF('Status'!$B$14=3,IF(ISNUMBER(L162),L162,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="6"/>
@@ -9692,6 +10223,9 @@
       <x:c r="S163" s="2" t="str">
         <x:f>IF(COUNTA(A163)=0,"",IF(COUNTIFS($A$6:$A$165,A163)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T163" s="23" t="str">
+        <x:f>IF(COUNTA($A163)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C163),C163,""),IF('Status'!$B$14=2,IF(ISNUMBER(D163),D163,""),IF('Status'!$B$14=3,IF(ISNUMBER(E163),E163,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J163),J163,""),IF('Status'!$B$14=2,IF(ISNUMBER(K163),K163,""),IF('Status'!$B$14=3,IF(ISNUMBER(L163),L163,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="6"/>
@@ -9747,6 +10281,9 @@
       <x:c r="S164" s="2" t="str">
         <x:f>IF(COUNTA(A164)=0,"",IF(COUNTIFS($A$6:$A$165,A164)&gt;1,"Duplicate target",""))</x:f>
       </x:c>
+      <x:c r="T164" s="23" t="str">
+        <x:f>IF(COUNTA($A164)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C164),C164,""),IF('Status'!$B$14=2,IF(ISNUMBER(D164),D164,""),IF('Status'!$B$14=3,IF(ISNUMBER(E164),E164,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J164),J164,""),IF('Status'!$B$14=2,IF(ISNUMBER(K164),K164,""),IF('Status'!$B$14=3,IF(ISNUMBER(L164),L164,""),""))),"")))</x:f>
+      </x:c>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="6"/>
@@ -9801,6 +10338,9 @@
       </x:c>
       <x:c r="S165" s="2" t="str">
         <x:f>IF(COUNTA(A165)=0,"",IF(COUNTIFS($A$6:$A$165,A165)&gt;1,"Duplicate target",""))</x:f>
+      </x:c>
+      <x:c r="T165" s="23" t="str">
+        <x:f>IF(COUNTA($A165)=0,"",IF('Status'!$B$13="MPS",IF('Status'!$B$14=1,IF(ISNUMBER(C165),C165,""),IF('Status'!$B$14=2,IF(ISNUMBER(D165),D165,""),IF('Status'!$B$14=3,IF(ISNUMBER(E165),E165,""),""))),IF('Status'!$B$13="PPS",IF('Status'!$B$14=1,IF(ISNUMBER(J165),J165,""),IF('Status'!$B$14=2,IF(ISNUMBER(K165),K165,""),IF('Status'!$B$14=3,IF(ISNUMBER(L165),L165,""),""))),"")))</x:f>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/runs/sample_1.xlsx
+++ b/runs/sample_1.xlsx
@@ -7,6 +7,7 @@
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estimates" sheetId="3" r:id="R1d720d84aca54612"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="4" r:id="R6973999336ec48c7"/>
   </x:sheets>
+  <x:calcPr fullCalcOnLoad="1"/>
 </x:workbook>
 </file>
 
@@ -464,7 +465,11 @@
       <x:c r="A4" s="2" t="str">
         <x:v>Official circuit ID</x:v>
       </x:c>
-      <x:c r="B4" s="6"/>
+      <x:c r="B4" s="6" t="inlineStr">
+        <x:is>
+          <x:t>S1</x:t>
+        </x:is>
+      </x:c>
       <x:c r="C4" s="2"/>
       <x:c r="D4" s="11" t="str">
         <x:v>Precision settings</x:v>
@@ -484,7 +489,9 @@
       <x:c r="A5" s="2" t="str">
         <x:v>Required qubits</x:v>
       </x:c>
-      <x:c r="B5" s="6"/>
+      <x:c r="B5" s="6" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="C5" s="2"/>
       <x:c r="D5" s="2" t="str">
         <x:v>MPS bond dimension χ</x:v>
@@ -1158,8 +1165,12 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="20"/>
-      <x:c r="B6" s="19"/>
+      <x:c r="A6" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B6" s="19" t="n">
+        <x:v>-0.3621922593901457</x:v>
+      </x:c>
       <x:c r="C6" s="14" t="str">
         <x:f>IF(OR(COUNTA($A6)=0,NOT(ISNUMBER('Status'!$E$5))),"",IF(COUNTIFS('Estimates'!$A$5:$A$2004,$A6,'Estimates'!$B$5:$B$2004,"MPS",'Estimates'!$C$5:$C$2004,'Status'!$E$5,'Estimates'!$H$5:$H$2004,1)=0,"",IF(COUNTIFS('Estimates'!$A$5:$A$2004,$A6,'Estimates'!$B$5:$B$2004,"MPS",'Estimates'!$C$5:$C$2004,'Status'!$E$5,'Estimates'!$H$5:$H$2004,1)&gt;1,"DUP",IF(COUNTIFS('Estimates'!$A$5:$A$2004,$A6,'Estimates'!$B$5:$B$2004,"MPS",'Estimates'!$C$5:$C$2004,'Status'!$E$5,'Estimates'!$H$5:$H$2004,1,'Estimates'!$F$5:$F$2004,"&lt;&gt;")=0,"",SUMIFS('Estimates'!$F$5:$F$2004,'Estimates'!$A$5:$A$2004,$A6,'Estimates'!$B$5:$B$2004,"MPS",'Estimates'!$C$5:$C$2004,'Status'!$E$5,'Estimates'!$H$5:$H$2004,1)))))</x:f>
       </x:c>
@@ -1214,8 +1225,12 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="20"/>
-      <x:c r="B7" s="19"/>
+      <x:c r="A7" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B7" s="19" t="n">
+        <x:v>-0.23266735629776267</x:v>
+      </x:c>
       <x:c r="C7" s="14" t="str">
         <x:f>IF(OR(COUNTA($A7)=0,NOT(ISNUMBER('Status'!$E$5))),"",IF(COUNTIFS('Estimates'!$A$5:$A$2004,$A7,'Estimates'!$B$5:$B$2004,"MPS",'Estimates'!$C$5:$C$2004,'Status'!$E$5,'Estimates'!$H$5:$H$2004,1)=0,"",IF(COUNTIFS('Estimates'!$A$5:$A$2004,$A7,'Estimates'!$B$5:$B$2004,"MPS",'Estimates'!$C$5:$C$2004,'Status'!$E$5,'Estimates'!$H$5:$H$2004,1)&gt;1,"DUP",IF(COUNTIFS('Estimates'!$A$5:$A$2004,$A7,'Estimates'!$B$5:$B$2004,"MPS",'Estimates'!$C$5:$C$2004,'Status'!$E$5,'Estimates'!$H$5:$H$2004,1,'Estimates'!$F$5:$F$2004,"&lt;&gt;")=0,"",SUMIFS('Estimates'!$F$5:$F$2004,'Estimates'!$A$5:$A$2004,$A7,'Estimates'!$B$5:$B$2004,"MPS",'Estimates'!$C$5:$C$2004,'Status'!$E$5,'Estimates'!$H$5:$H$2004,1)))))</x:f>
       </x:c>
@@ -1270,8 +1285,12 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="20"/>
-      <x:c r="B8" s="19"/>
+      <x:c r="A8" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B8" s="19" t="n">
+        <x:v>0.10250411538796315</x:v>
+      </x:c>
       <x:c r="C8" s="14" t="str">
         <x:f>IF(OR(COUNTA($A8)=0,NOT(ISNUMBER('Status'!$E$5))),"",IF(COUNTIFS('Estimates'!$A$5:$A$2004,$A8,'Estimates'!$B$5:$B$2004,"MPS",'Estimates'!$C$5:$C$2004,'Status'!$E$5,'Estimates'!$H$5:$H$2004,1)=0,"",IF(COUNTIFS('Estimates'!$A$5:$A$2004,$A8,'Estimates'!$B$5:$B$2004,"MPS",'Estimates'!$C$5:$C$2004,'Status'!$E$5,'Estimates'!$H$5:$H$2004,1)&gt;1,"DUP",IF(COUNTIFS('Estimates'!$A$5:$A$2004,$A8,'Estimates'!$B$5:$B$2004,"MPS",'Estimates'!$C$5:$C$2004,'Status'!$E$5,'Estimates'!$H$5:$H$2004,1,'Estimates'!$F$5:$F$2004,"&lt;&gt;")=0,"",SUMIFS('Estimates'!$F$5:$F$2004,'Estimates'!$A$5:$A$2004,$A8,'Estimates'!$B$5:$B$2004,"MPS",'Estimates'!$C$5:$C$2004,'Status'!$E$5,'Estimates'!$H$5:$H$2004,1)))))</x:f>
       </x:c>
@@ -1326,8 +1345,12 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="20"/>
-      <x:c r="B9" s="19"/>
+      <x:c r="A9" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B9" s="19" t="n">
+        <x:v>-0.10937094850563352</x:v>
+      </x:c>
       <x:c r="C9" s="14" t="str">
         <x:f>IF(OR(COUNTA($A9)=0,NOT(ISNUMBER('Status'!$E$5))),"",IF(COUNTIFS('Estimates'!$A$5:$A$2004,$A9,'Estimates'!$B$5:$B$2004,"MPS",'Estimates'!$C$5:$C$2004,'Status'!$E$5,'Estimates'!$H$5:$H$2004,1)=0,"",IF(COUNTIFS('Estimates'!$A$5:$A$2004,$A9,'Estimates'!$B$5:$B$2004,"MPS",'Estimates'!$C$5:$C$2004,'Status'!$E$5,'Estimates'!$H$5:$H$2004,1)&gt;1,"DUP",IF(COUNTIFS('Estimates'!$A$5:$A$2004,$A9,'Estimates'!$B$5:$B$2004,"MPS",'Estimates'!$C$5:$C$2004,'Status'!$E$5,'Estimates'!$H$5:$H$2004,1,'Estimates'!$F$5:$F$2004,"&lt;&gt;")=0,"",SUMIFS('Estimates'!$F$5:$F$2004,'Estimates'!$A$5:$A$2004,$A9,'Estimates'!$B$5:$B$2004,"MPS",'Estimates'!$C$5:$C$2004,'Status'!$E$5,'Estimates'!$H$5:$H$2004,1)))))</x:f>
       </x:c>
@@ -18404,52 +18427,140 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="6"/>
-      <x:c r="B5" s="6"/>
+      <x:c r="A5" s="6" t="inlineStr">
+        <x:is>
+          <x:t>bzMWdutLEuLfGnQS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Exact</x:t>
+        </x:is>
+      </x:c>
       <x:c r="C5" s="6"/>
       <x:c r="D5" s="12"/>
       <x:c r="E5" s="6"/>
-      <x:c r="F5" s="6"/>
-      <x:c r="G5" s="6"/>
-      <x:c r="H5" s="8"/>
-      <x:c r="I5" s="8"/>
-      <x:c r="J5" s="6"/>
+      <x:c r="F5" s="6" t="inlineStr">
+        <x:is>
+          <x:t>succeeded</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G5" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H5" s="8" t="n">
+        <x:v>0.028</x:v>
+      </x:c>
+      <x:c r="I5" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J5" s="6" t="inlineStr">
+        <x:is>
+          <x:t>runner bb469474b4465930605b</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="6"/>
-      <x:c r="B6" s="6"/>
+      <x:c r="A6" s="6" t="inlineStr">
+        <x:is>
+          <x:t>vTlWoGMG8HxiH52f</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Exact</x:t>
+        </x:is>
+      </x:c>
       <x:c r="C6" s="6"/>
       <x:c r="D6" s="12"/>
       <x:c r="E6" s="6"/>
-      <x:c r="F6" s="6"/>
-      <x:c r="G6" s="6"/>
-      <x:c r="H6" s="8"/>
-      <x:c r="I6" s="8"/>
-      <x:c r="J6" s="6"/>
+      <x:c r="F6" s="6" t="inlineStr">
+        <x:is>
+          <x:t>succeeded</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G6" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H6" s="8" t="n">
+        <x:v>0.026</x:v>
+      </x:c>
+      <x:c r="I6" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J6" s="6" t="inlineStr">
+        <x:is>
+          <x:t>runner 10c92b505fbedaf6373c</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="6"/>
-      <x:c r="B7" s="6"/>
+      <x:c r="A7" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Ny0FhXGKFn1WFvJ0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Exact</x:t>
+        </x:is>
+      </x:c>
       <x:c r="C7" s="6"/>
       <x:c r="D7" s="12"/>
       <x:c r="E7" s="6"/>
-      <x:c r="F7" s="6"/>
-      <x:c r="G7" s="6"/>
-      <x:c r="H7" s="8"/>
-      <x:c r="I7" s="8"/>
-      <x:c r="J7" s="6"/>
+      <x:c r="F7" s="6" t="inlineStr">
+        <x:is>
+          <x:t>succeeded</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G7" s="6" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H7" s="8" t="n">
+        <x:v>0.028</x:v>
+      </x:c>
+      <x:c r="I7" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J7" s="6" t="inlineStr">
+        <x:is>
+          <x:t>runner 332f7a15fd5250cc3086</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="6"/>
-      <x:c r="B8" s="6"/>
+      <x:c r="A8" s="6" t="inlineStr">
+        <x:is>
+          <x:t>gEJuPUHl9fnY1QIE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Exact</x:t>
+        </x:is>
+      </x:c>
       <x:c r="C8" s="6"/>
       <x:c r="D8" s="12"/>
       <x:c r="E8" s="6"/>
-      <x:c r="F8" s="6"/>
-      <x:c r="G8" s="6"/>
-      <x:c r="H8" s="8"/>
-      <x:c r="I8" s="8"/>
-      <x:c r="J8" s="6"/>
+      <x:c r="F8" s="6" t="inlineStr">
+        <x:is>
+          <x:t>succeeded</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G8" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H8" s="8" t="n">
+        <x:v>0.027</x:v>
+      </x:c>
+      <x:c r="I8" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J8" s="6" t="inlineStr">
+        <x:is>
+          <x:t>runner 21cb152ac4c675dacf09</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="6"/>
